--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -87,6 +88,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,7 +525,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7755448.98377343</v>
+        <v>7664508.347600595</v>
       </c>
     </row>
     <row r="10">
@@ -539,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>7789700.04845872</v>
+        <v>7698759.412285886</v>
       </c>
     </row>
     <row r="13">
@@ -561,7 +563,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>7755448.98377343</v>
+        <v>7664508.347600595</v>
       </c>
     </row>
     <row r="15">
@@ -571,7 +573,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2316305.234750267</v>
+        <v>-2407245.870923101</v>
       </c>
     </row>
     <row r="16">
@@ -619,13 +621,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-7755448.98377343</v>
+        <v>-7664508.347600595</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-2610119.023505832</v>
+        <v>-2519178.387332997</v>
       </c>
     </row>
     <row r="25">
@@ -660,7 +662,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-05T13:02:39+00:00</t>
+          <t>2026-06-08T14:48:50+00:00</t>
         </is>
       </c>
     </row>
@@ -816,7 +818,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread)</t>
+          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread + agent rate)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -857,13 +859,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1410297.398875481</v>
+        <v>1597516.094726083</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1410297.398875481</v>
+        <v>1597516.094726083</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-1410297.398875481</v>
+        <v>-1597516.094726083</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -922,13 +924,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1247772.842824006</v>
+        <v>1413416.20608737</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1247772.842824006</v>
+        <v>1413416.20608737</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1577227.157175994</v>
+        <v>1411583.79391263</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -987,13 +989,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1084588.685060978</v>
+        <v>1228569.152807245</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1084588.685060978</v>
+        <v>1228569.152807245</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>168509.8887462882</v>
+        <v>24529.42100002097</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>90251565.90411383</v>
@@ -1056,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>555388.0738366774</v>
+        <v>629116.5164740883</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>555388.0738366774</v>
+        <v>629116.5164740883</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>163027.4065503575</v>
+        <v>89298.96391294656</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>69623450.80112581</v>
@@ -1125,13 +1127,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>534627.5561025015</v>
+        <v>605600.0147478303</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>534627.5561025015</v>
+        <v>605600.0147478303</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-122182.7591005014</v>
+        <v>-193155.2177458303</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1144,82 +1146,82 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
+          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>207131500.431691</v>
+        <v>196264917.5470026</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>287780830.420175</v>
+        <v>196856311.4279603</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>80649329.988484</v>
+        <v>591393.88095773</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-627039.8278228145</v>
+        <v>0</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-627039.8278228145</v>
+        <v>0</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>207131500.431691</v>
+        <v>196264917.5470026</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>492335.6524278345</v>
+        <v>528435.9418512845</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>492335.6524278345</v>
+        <v>483335.5566696879</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-1119375.480250649</v>
+        <v>-528435.9418512845</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>0</v>
+        <v>45100.3851815965</v>
       </c>
       <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1228,58 +1230,58 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>196264917.5470026</v>
+        <v>100000608.9318128</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>196856311.4279603</v>
+        <v>200002600.606636</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>591393.88095773</v>
+        <v>100001991.6748231</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0</v>
+        <v>582414.4362051206</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0</v>
+        <v>582414.4362051206</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>196264917.5470026</v>
+        <v>171163998.3359494</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>466506.6203248271</v>
+        <v>460852.656716032</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>421406.2351432306</v>
+        <v>460852.656716032</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-466506.6203248271</v>
+        <v>121561.7794890887</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>45100.3851815965</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1289,44 +1291,44 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>100000608.9318128</v>
+        <v>100000425.5500491</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>200002600.606636</v>
+        <v>100000617.7417743</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>100001991.6748231</v>
+        <v>192.1917252263534</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>582414.4362051206</v>
+        <v>12826.64968891759</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>582414.4362051206</v>
+        <v>12826.64968891759</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>171163998.3359494</v>
+        <v>99999974.31940752</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>406843.6650980448</v>
+        <v>269246.186608593</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>406843.6650980448</v>
+        <v>269246.186608593</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>175570.7711070759</v>
+        <v>-256419.5369196754</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1339,12 +1341,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
+          <t>Spark PYUSD (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1354,44 +1356,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>120038508.359851</v>
+        <v>99995755.66040599</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>387977397.421864</v>
+        <v>100000062.958447</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>267938889.062013</v>
+        <v>4307.298041</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-742151.6061946489</v>
+        <v>61312.987037</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-742151.6061946489</v>
+        <v>61312.987037</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>120038508.359851</v>
+        <v>99993719.74294186</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>285322.3059102079</v>
+        <v>269229.346395646</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>285322.3059102079</v>
+        <v>269229.346395646</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-1027473.912104857</v>
+        <v>-207916.359358646</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1404,189 +1406,189 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
+          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>100000425.5500491</v>
+        <v>101106912.9085265</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>100000617.7417743</v>
+        <v>101411572.6019855</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>192.1917252263534</v>
+        <v>304659.6934590152</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>12826.64968891759</v>
+        <v>0</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>12826.64968891759</v>
+        <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>99999974.31940752</v>
+        <v>101106912.9085265</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>237692.2510419834</v>
+        <v>272226.5773132768</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>237692.2510419834</v>
+        <v>248992.874756096</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-224865.6013530658</v>
+        <v>-272226.5773132768</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>0</v>
+        <v>23233.70255718082</v>
       </c>
       <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spark PYUSD (SparkLend spToken)</t>
+          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>99995755.66040599</v>
+        <v>75079284.39269957</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>100000062.958447</v>
+        <v>75305516.51778577</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4307.298041</v>
+        <v>226232.1250862077</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>61312.987037</v>
+        <v>0</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>61312.987037</v>
+        <v>0</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>99993719.74294186</v>
+        <v>75079284.39269957</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>237677.3843945712</v>
+        <v>202148.1620732098</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>237677.3843945712</v>
+        <v>184895.4370952043</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-176364.3973575712</v>
+        <v>-202148.1620732098</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>0</v>
+        <v>17252.72497800558</v>
       </c>
       <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+          <t>Spark USDC (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>95656876.179346</v>
+        <v>43659321.092129</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>152857139.195815</v>
+        <v>47958113.065451</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>57200263.016469</v>
+        <v>4298791.973322</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-387026.4406245563</v>
+        <v>103808.620787</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-387026.4406245563</v>
+        <v>103808.620787</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>95656876.179346</v>
+        <v>43809141.92614811</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>227369.0406568471</v>
+        <v>117954.4743135079</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>227369.0406568471</v>
+        <v>117954.4743135079</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-614395.4812814033</v>
+        <v>-14145.85352650795</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1599,17 +1601,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1618,78 +1620,70 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>101106912.9085265</v>
+        <v>0</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>101411572.6019855</v>
+        <v>55000541.20928549</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>304659.6934590152</v>
+        <v>55000541.20928549</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0</v>
+        <v>101946.981441214</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0</v>
+        <v>101946.981441214</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>101106912.9085265</v>
+        <v>33362863.83401008</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>240323.3589677968</v>
+        <v>89828.26168491939</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>217089.6564106159</v>
+        <v>89828.26168491939</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>-240323.3589677968</v>
+        <v>12118.71975629463</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>23233.70255718082</v>
+        <v>0</v>
       </c>
       <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>SPREAD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" s="6" t="n">
-        <v>75079284.39269957</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>75305516.51778577</v>
+        <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>226232.1250862077</v>
+        <v>0</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>0</v>
@@ -1704,37 +1698,41 @@
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>75079284.39269957</v>
+        <v>0</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>178457.6869682115</v>
+        <v>0</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>161204.9619902059</v>
+        <v>-55265.60425743128</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>-178457.6869682115</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>17252.72497800558</v>
-      </c>
-      <c r="S15" t="inlineStr"/>
+        <v>55265.60425743128</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spark USDC (SparkLend spToken)</t>
+          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1744,44 +1742,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>43659321.092129</v>
+        <v>15106645.23632516</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>47958113.065451</v>
+        <v>10113369.18090356</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>4298791.973322</v>
+        <v>-4993276.0554216</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>103808.620787</v>
+        <v>58464.15865458552</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>103808.620787</v>
+        <v>58464.15865458552</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>43809141.92614811</v>
+        <v>13122033.00936666</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>104130.9623478868</v>
+        <v>35330.58255634345</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>104130.9623478868</v>
+        <v>35330.58255634345</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-322.3415608868459</v>
+        <v>23133.57609824207</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1794,12 +1792,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1809,239 +1807,243 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0</v>
+        <v>49999911.74966041</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>55000541.20928549</v>
+        <v>50000340.64647674</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>55000541.20928549</v>
+        <v>428.8968163312471</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>101946.981441214</v>
+        <v>34251.0646852904</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>101946.981441214</v>
+        <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0</v>
+        <v>34251.0646852904</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>33362863.83401008</v>
+        <v>49998703.81509366</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>79300.96242408732</v>
+        <v>0</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>79300.96242408732</v>
+        <v>34251.0646852904</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>22646.01901712669</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0</v>
+        <v>49998703.81509366</v>
       </c>
       <c r="R17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SPREAD</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>avalanche_c</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="n">
-        <v>0</v>
+        <v>10000965.036792</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0</v>
+        <v>10000143.505486</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0</v>
+        <v>-821.531306</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0</v>
+        <v>19422.097364</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0</v>
+        <v>19422.097364</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0</v>
+        <v>10000242.05005379</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0</v>
+        <v>26925.27728596954</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>-55265.60425743128</v>
+        <v>26925.27728596954</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0</v>
+        <v>-7503.179921969538</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>55265.60425743128</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>49999911.74966041</v>
+        <v>4994817.315553</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>50000340.64647674</v>
+        <v>4983790.597531</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>428.8968163312471</v>
+        <v>-11026.718022</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>34251.0646852904</v>
+        <v>-5.6402e-09</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0</v>
+        <v>-5.6402e-09</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>34251.0646852904</v>
+        <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>49998703.81509366</v>
+        <v>5050529.234246395</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0</v>
+        <v>13598.36085890023</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>34251.0646852904</v>
+        <v>13598.36085890023</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0</v>
+        <v>-13598.36085890587</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>49998703.81509366</v>
+        <v>0</v>
       </c>
       <c r="R19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>15106645.23632516</v>
+        <v>4979093.435761</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>10113369.18090356</v>
+        <v>5000000</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-4993276.0554216</v>
+        <v>20906.564239</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>58464.15865458552</v>
+        <v>2.1207e-09</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>58464.15865458552</v>
+        <v>2.1207e-09</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>13122033.00936666</v>
+        <v>5011688.25004375</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>31190.06365222887</v>
+        <v>13493.78296323714</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>31190.06365222887</v>
+        <v>13493.78296323714</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>27274.09500235666</v>
+        <v>-13493.78296323501</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2054,59 +2056,59 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>10000965.036792</v>
+        <v>5000000</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>10000143.505486</v>
+        <v>4997665.827264</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-821.531306</v>
+        <v>-2334.172736</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>19422.097364</v>
+        <v>1.013e-10</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>19422.097364</v>
+        <v>1.013e-10</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>10000242.05005379</v>
+        <v>4984668.082129179</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>23769.80654264698</v>
+        <v>13421.03217282908</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>23769.80654264698</v>
+        <v>13421.03217282908</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-4347.709178646983</v>
+        <v>-13421.03217282898</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2119,17 +2121,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2138,40 +2140,40 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>4994817.315553</v>
+        <v>5000000</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>4983790.597531</v>
+        <v>5000000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-11026.718022</v>
+        <v>0</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-5.6402e-09</v>
+        <v>-2.4963e-09</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-5.6402e-09</v>
+        <v>-2.4963e-09</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>5050529.234246395</v>
+        <v>4915994.634819037</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>12004.71970929685</v>
+        <v>13236.13148725027</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12004.71970929685</v>
+        <v>13236.13148725027</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-12004.71970930249</v>
+        <v>-13236.13148725277</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2184,59 +2186,59 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>Spark Blue Chip USDC Vault (Morpho)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4979093.435761</v>
+        <v>976334.4376037563</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>5000000</v>
+        <v>977613.8365042645</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>20906.564239</v>
+        <v>1279.398900508137</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2.1207e-09</v>
+        <v>2260.871717804608</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>2.1207e-09</v>
+        <v>2260.871717804608</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>5011688.25004375</v>
+        <v>975739.8384111297</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11912.39767590988</v>
+        <v>2627.142980808697</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11912.39767590988</v>
+        <v>2627.142980808697</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11912.39767590775</v>
+        <v>-366.2712630040895</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2249,12 +2251,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2264,67 +2266,67 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>5000000</v>
+        <v>973415.2506528809</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>4997665.827264</v>
+        <v>976348.3873033939</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-2334.172736</v>
+        <v>2933.13665051312</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>1.013e-10</v>
+        <v>0</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>1.013e-10</v>
+        <v>0</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4984668.082129179</v>
+        <v>973415.2506528809</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>11848.17281406508</v>
+        <v>2620.884115307928</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>11848.17281406508</v>
+        <v>2397.199702959646</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-11848.17281406498</v>
+        <v>-2620.884115307928</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>0</v>
+        <v>223.6844123482817</v>
       </c>
       <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2333,40 +2335,40 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-2.4963e-09</v>
+        <v>-9e-11</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-2.4963e-09</v>
+        <v>-9e-11</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>4915994.634819037</v>
+        <v>69404.94659889408</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>11684.94130936666</v>
+        <v>186.8702200246323</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>11684.94130936666</v>
+        <v>186.8702200246323</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-11684.94130936916</v>
+        <v>-186.8702200247224</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2379,12 +2381,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDC Vault (Morpho)</t>
+          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2394,44 +2396,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>976334.4376037563</v>
+        <v>0</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>977613.8365042645</v>
+        <v>1868.74164</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>1279.398900508137</v>
+        <v>1868.74164</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>2260.871717804608</v>
+        <v>-2.18382e-08</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>2260.871717804608</v>
+        <v>-2.18382e-08</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>975739.8384111297</v>
+        <v>538.7469580157663</v>
       </c>
       <c r="M26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2319.25858183217</v>
+        <v>1.450556012438627</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2319.25858183217</v>
+        <v>1.450556012438627</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-58.38686402756296</v>
+        <v>-1.450556034276827</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2444,17 +2446,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2463,58 +2465,58 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>973415.2506528809</v>
+        <v>61.15121926789406</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>976348.3873033939</v>
+        <v>494.7150552250027</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>2933.13665051312</v>
+        <v>433.5638359571087</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0</v>
+        <v>1.217080133914307</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0</v>
+        <v>1.217080133914307</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>973415.2506528809</v>
+        <v>499.1597379746905</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2313.733215443196</v>
+        <v>1.343968904721477</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2090.048803094914</v>
+        <v>1.343968904721477</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-2313.733215443196</v>
+        <v>-0.1268887708071693</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>223.6844123482817</v>
+        <v>0</v>
       </c>
       <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2524,44 +2526,44 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>285387.136685</v>
+        <v>332.9212943539781</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>94443.720094</v>
+        <v>344.9608587271188</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-190943.416591</v>
+        <v>12.0395643731406</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-574.4713114756599</v>
+        <v>1.26224901053333</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-574.4713114756599</v>
+        <v>1.26224901053333</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>285387.136685</v>
+        <v>336.3854314348162</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>678.3432835734128</v>
+        <v>0.905705179035562</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>678.3432835734128</v>
+        <v>0.905705179035562</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-1252.814595049073</v>
+        <v>0.3565438314977682</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2574,59 +2576,59 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-9e-11</v>
+        <v>0</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-9e-11</v>
+        <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>69404.94659889408</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>164.9702222707283</v>
+        <v>0.7643827127248842</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>164.9702222707283</v>
+        <v>0.7643827127248842</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-164.9702222708183</v>
+        <v>-0.7643827127248842</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2639,12 +2641,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2654,44 +2656,44 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0</v>
+        <v>98.60727406618892</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1868.74164</v>
+        <v>98.88131626312872</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>1868.74164</v>
+        <v>0.2740421969397932</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-2.18382e-08</v>
+        <v>0.2740421969397932</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-2.18382e-08</v>
+        <v>0.2740421969397932</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>538.7469580157663</v>
+        <v>98.60727406618892</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>1.280560100783305</v>
+        <v>0.2654963933229446</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>1.280560100783305</v>
+        <v>0.2654963933229446</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-1.280560122621505</v>
+        <v>0.008545803616848612</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2704,17 +2706,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2723,40 +2725,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>61.15121926789406</v>
+        <v>21.90604334087989</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>494.7150552250027</v>
+        <v>21.90659475982325</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>433.5638359571087</v>
+        <v>0.0005514189433507683</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>1.217080133914307</v>
+        <v>1.025604740466448e-05</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>1.217080133914307</v>
+        <v>1.025604740466448e-05</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>499.1597379746905</v>
+        <v>21.90648786754442</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>1.186464322178375</v>
+        <v>0.0589823983502668</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.186464322178375</v>
+        <v>0.0589823983502668</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.03061581173593191</v>
+        <v>-0.05897214230286214</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2769,12 +2771,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2784,44 +2786,44 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>332.9212943539781</v>
+        <v>1.210584</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>344.9608587271188</v>
+        <v>1.210594</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>12.0395643731406</v>
+        <v>1e-05</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>1.26224901053333</v>
+        <v>1e-05</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>1.26224901053333</v>
+        <v>1e-05</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>336.3854314348162</v>
+        <v>1.210584</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.7995623094870405</v>
+        <v>0.003259452092740379</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.7995623094870405</v>
+        <v>0.003259452092740379</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.4626867010462897</v>
+        <v>-0.003249452092740379</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2834,59 +2836,59 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>0.057354</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>0.057463</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0</v>
+        <v>0.000109</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0</v>
+        <v>0.000109</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0</v>
+        <v>0.000109</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>0.057354</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.6748019347411506</v>
+        <v>0.0001544234975243615</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.6748019347411506</v>
+        <v>0.0001544234975243615</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.6748019347411506</v>
+        <v>-4.542349752436153e-05</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2899,59 +2901,59 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>98.60727406618892</v>
+        <v>0.00631</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>98.88131626312872</v>
+        <v>0.006319</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.2740421969397932</v>
+        <v>9e-06</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.2740421969397932</v>
+        <v>9e-06</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.2740421969397932</v>
+        <v>9e-06</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>98.60727406618892</v>
+        <v>0.00631</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.2343819096097254</v>
+        <v>1.698943873799075e-05</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2343819096097254</v>
+        <v>1.698943873799075e-05</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.03966028733006779</v>
+        <v>-7.989438737990746e-06</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2964,12 +2966,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2979,44 +2981,44 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>21.90604334087989</v>
+        <v>0.005739369858543872</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>21.90659475982325</v>
+        <v>0.005740696354252308</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.0005514189433507683</v>
+        <v>1.326495708436e-06</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1.025604740466448e-05</v>
+        <v>1.326495708436e-06</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>1.025604740466448e-05</v>
+        <v>1.326495708436e-06</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>21.90648786754442</v>
+        <v>0.005739369858543872</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.05207003750849946</v>
+        <v>1.545303844792421e-05</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.05207003750849946</v>
+        <v>1.545303844792421e-05</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.05205978146109479</v>
+        <v>-1.41265427394882e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3029,59 +3031,59 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>1.210584</v>
+        <v>0.001688</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>1.210594</v>
+        <v>0.001692</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>1e-05</v>
+        <v>4e-06</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>1e-05</v>
+        <v>4e-06</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>1e-05</v>
+        <v>4e-06</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>1.210584</v>
+        <v>0.001688</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.00287746509930417</v>
+        <v>4.544876797104339e-06</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.00287746509930417</v>
+        <v>4.544876797104339e-06</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-0.00286746509930417</v>
+        <v>-5.448767971043391e-07</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3094,12 +3096,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3109,44 +3111,44 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.057354</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.057463</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.000109</v>
+        <v>0</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.000109</v>
+        <v>0</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0.000109</v>
+        <v>0</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.057354</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.0001363260486719562</v>
+        <v>3.339043091263772e-06</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.0001363260486719562</v>
+        <v>3.339043091263772e-06</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-2.732604867195616e-05</v>
+        <v>-3.339043091263772e-06</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3159,17 +3161,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3178,40 +3180,40 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.00631</v>
+        <v>0.000518423030497757</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.006319</v>
+        <v>0.000519245328957253</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>9e-06</v>
+        <v>8.22298459496e-07</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>9e-06</v>
+        <v>8.22298459495e-07</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>9e-06</v>
+        <v>8.22298459495e-07</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.00631</v>
+        <v>0.000518423030497757</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.499838489242326e-05</v>
+        <v>1.395834598574509e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.499838489242326e-05</v>
+        <v>1.395834598574509e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-5.998384892423255e-06</v>
+        <v>-5.73536139079509e-07</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3224,12 +3226,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3239,44 +3241,44 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.005739369858543872</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.005740696354252308</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>1.326495708436e-06</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>1.326495708436e-06</v>
+        <v>0</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>1.326495708436e-06</v>
+        <v>0</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.005739369858543872</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.364204091575496e-05</v>
+        <v>2.016554185529916e-07</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.364204091575496e-05</v>
+        <v>2.016554185529916e-07</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-1.231554520731896e-05</v>
+        <v>-2.016554185529916e-07</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3289,17 +3291,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3308,40 +3310,40 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.001688</v>
+        <v>0</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.001692</v>
+        <v>0</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.001688</v>
+        <v>0</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>4.012246227957283e-06</v>
+        <v>0</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>4.012246227957283e-06</v>
+        <v>0</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-1.224622795728285e-08</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3354,12 +3356,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3373,10 +3375,10 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>0</v>
@@ -3394,19 +3396,19 @@
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.947728540506426e-06</v>
+        <v>0</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>2.947728540506426e-06</v>
+        <v>0</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-2.947728540506426e-06</v>
+        <v>0</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3419,12 +3421,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3434,44 +3436,44 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0.000518423030497757</v>
+        <v>0</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0.000519245328957253</v>
+        <v>0</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>8.22298459496e-07</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>8.22298459495e-07</v>
+        <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>8.22298459495e-07</v>
+        <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.000518423030497757</v>
+        <v>0</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.232251687559721e-06</v>
+        <v>0</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.232251687559721e-06</v>
+        <v>0</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-4.09953228064721e-07</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3484,12 +3486,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3499,14 +3501,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>0</v>
@@ -3524,19 +3526,19 @@
         <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1.780226898453839e-07</v>
+        <v>0</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1.780226898453839e-07</v>
+        <v>0</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.780226898453839e-07</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3549,12 +3551,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3564,7 +3566,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
@@ -3592,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" s="6" t="n">
         <v>0</v>
@@ -3609,17 +3611,21 @@
       <c r="R44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3629,7 +3635,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
@@ -3679,12 +3685,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3694,7 +3700,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
@@ -3707,13 +3713,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0</v>
+        <v>891779.9999999979</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0</v>
+        <v>891779.9999999979</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -3731,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0</v>
+        <v>891779.9999999979</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3744,12 +3750,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3759,7 +3765,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3772,13 +3778,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0</v>
+        <v>4.3675e-08</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0</v>
+        <v>4.3675e-08</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
@@ -3796,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0</v>
+        <v>4.3675e-08</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3809,12 +3815,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3824,7 +3830,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -3837,19 +3843,19 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0</v>
+        <v>-4.7472e-08</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0</v>
+        <v>-4.7472e-08</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0</v>
+        <v>21.29666254724045</v>
       </c>
       <c r="M48" s="7" t="n">
         <v>0</v>
@@ -3861,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0</v>
+        <v>-4.7472e-08</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3871,36 +3877,36 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>SDE (fixed)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -3918,10 +3924,10 @@
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3933,32 +3939,36 @@
         <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3971,13 +3981,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>891779.9999999979</v>
+        <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>891779.9999999979</v>
+        <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
@@ -3995,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>891779.9999999979</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
@@ -4008,17 +4018,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4027,31 +4037,31 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>4.3675e-08</v>
+        <v>0</v>
       </c>
       <c r="I51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>4.3675e-08</v>
+        <v>0</v>
       </c>
       <c r="K51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0</v>
@@ -4060,30 +4070,34 @@
         <v>0</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>4.3675e-08</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S48</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>USDS raw (Optimism — POL)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4092,28 +4106,28 @@
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-4.7472e-08</v>
+        <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-4.7472e-08</v>
+        <v>0</v>
       </c>
       <c r="K52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>21.29666254724045</v>
+        <v>89900000</v>
       </c>
       <c r="M52" s="7" t="n">
         <v>0</v>
@@ -4125,10 +4139,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>-4.7472e-08</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>21.29666254724045</v>
+        <v>89900000</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
@@ -4142,17 +4156,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>USDS raw (Unichain — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4161,10 +4175,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4182,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4197,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4211,50 +4225,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0</v>
+        <v>207131500.431691</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0</v>
+        <v>287780830.420175</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0</v>
+        <v>80649329.988484</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0</v>
+        <v>-627039.8278228145</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0</v>
+        <v>-627039.8278228145</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0</v>
+        <v>207131500.431691</v>
       </c>
       <c r="M54" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" s="6" t="n">
         <v>0</v>
@@ -4263,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0</v>
+        <v>-627039.8278228145</v>
       </c>
       <c r="Q54" s="6" t="n">
         <v>0</v>
@@ -4271,52 +4285,56 @@
       <c r="R54" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S57</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>Spark Savings V2 — spUSDT vault</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>90000000</v>
+        <v>120038508.359851</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>90000000</v>
+        <v>387977397.421864</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0</v>
+        <v>267938889.062013</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0</v>
+        <v>-742151.6061946489</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0</v>
+        <v>-742151.6061946489</v>
       </c>
       <c r="K55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>90000000</v>
+        <v>120038508.359851</v>
       </c>
       <c r="M55" s="7" t="n">
         <v>0</v>
@@ -4328,64 +4346,64 @@
         <v>0</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0</v>
+        <v>-742151.6061946489</v>
       </c>
       <c r="Q55" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="R55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>Spark Savings V2 — spPYUSD vault</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>89900000</v>
+        <v>285387.136685</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>89900000</v>
+        <v>94443.720094</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0</v>
+        <v>-190943.416591</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0</v>
+        <v>-574.4713114756599</v>
       </c>
       <c r="I56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0</v>
+        <v>-574.4713114756599</v>
       </c>
       <c r="K56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>89900000</v>
+        <v>285387.136685</v>
       </c>
       <c r="M56" s="7" t="n">
         <v>0</v>
@@ -4397,64 +4415,64 @@
         <v>0</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0</v>
+        <v>-574.4713114756599</v>
       </c>
       <c r="Q56" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S60</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>89900000</v>
+        <v>95656876.179346</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>89900000</v>
+        <v>152857139.195815</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0</v>
+        <v>57200263.016469</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0</v>
+        <v>-387026.4406245563</v>
       </c>
       <c r="I57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0</v>
+        <v>-387026.4406245563</v>
       </c>
       <c r="K57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>89900000</v>
+        <v>95656876.179346</v>
       </c>
       <c r="M57" s="7" t="n">
         <v>0</v>
@@ -4466,17 +4484,17 @@
         <v>0</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0</v>
+        <v>-387026.4406245563</v>
       </c>
       <c r="Q57" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4603,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7755448.98377343</v>
+        <v>7664508.347600595</v>
       </c>
     </row>
     <row r="5">
@@ -4605,7 +4623,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7789700.04845872</v>
+        <v>7698759.412285886</v>
       </c>
     </row>
     <row r="8">
@@ -4632,7 +4650,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>7755448.98377343</v>
+        <v>7664508.347600595</v>
       </c>
     </row>
     <row r="12">
@@ -4642,7 +4660,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-2316305.234750267</v>
+        <v>-2407245.870923101</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -4937,4 +4955,1522 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Daily ilk debt + Sky charge breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>cum_debt</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>− ALM idle</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>− PSM USDS</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>− SDE NAV</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>− Curve idle</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>− Lending idle</t>
+        </is>
+      </c>
+      <c r="H5" s="2">
+        <f> utilized</f>
+        <v/>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>SSR APY</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>base APY</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>T (months)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>ref_rate APY</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>sub APY</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge (gross on cum_debt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>3159527983.465951</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>44911720.79857019</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>70289118.90880118</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>53443795.92462372</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>222761546.1543027</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2433151801.679653</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>281436.7600742012</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>365454.9290416628</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>3108979150.764832</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>42264739.63239259</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>70082020.93708614</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>60874882.1318847</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>202280884.9245871</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>2398506623.138882</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>277429.4364070235</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>359608.0683192389</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>3139557721.076495</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>45903618.77129755</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>71919290.05995171</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>56917531.56825144</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>205373147.2248062</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>2424474133.452188</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>280433.0352637514</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>363145.0172881749</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>3141266002.661607</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>50573746.36953703</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>72165573.01717961</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>59127098.93596155</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>199490512.222793</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2424939072.116136</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>280486.8135899226</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>363342.6100706212</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>3053995867.48157</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>49019765.63915107</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>71955022.75225696</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>74193559.24762456</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>168645198.529759</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2355212321.312778</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>272421.6896535321</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>353248.2854668903</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>2984358626.829742</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>43420025.24945795</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>70093687.03120825</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>62663404.50552572</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>139389471.4291162</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>2333822038.614434</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>269947.5275993859</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>345193.5149523549</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>2973910687.81137</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>43331747.98936062</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>69404974.57314776</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>56117349.84955318</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>137059463.4132225</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2333027151.986086</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>269855.5849934399</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>343985.0272185631</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>2973897203.641477</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>42972324.58983186</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>69296818.10221891</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>44993194.46390114</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>136750375.5576032</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>2344914490.927922</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>271230.5646208453</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>343983.4675373774</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>3092551877.583306</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>42899555.11684096</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>68988108.87019685</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>61607865.93892223</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>131807128.8914069</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>2452279218.765939</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>283649.1819582925</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>357707.9655234039</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>3109481334.50664</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>42923510.8116744</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>69468489.83052413</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>56661540.26184572</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>136841950.8508666</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2468615842.751729</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>285538.7995817952</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>359666.1546931178</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>3145504400.532222</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>66366024.4559039</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>69840737.56294712</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>63224001.35398827</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>142782678.6256742</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2468320958.533709</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>285504.691040413</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>363832.8552595108</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>3136818758.084431</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>65825302.58991265</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>70258797.83252665</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>52662079.36682548</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>138982244.1528277</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>2474120334.142338</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>286175.4907334776</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>362828.208090361</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>3148361751.906786</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>66204220.05029075</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>69557060.69633225</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>42287173.46979559</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>142368665.4817924</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2492974632.208575</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>288356.32160378</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>364163.3581540263</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>3118135878.924826</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>66237408.33460446</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>69255485.04462956</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>53265841.76145346</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>139402138.7763296</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>2455005005.007809</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>283964.4670334108</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>360667.2048287037</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>3087993177.392972</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>66140189.59027819</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>69605286.29178502</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>53138187.3806347</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>136407246.0004658</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>2427732268.129808</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>280809.8957896429</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>357180.6717430357</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>3158960204.002114</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>65730562.95242047</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>69323084.617901</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>47401363.76374279</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>136793539.1491862</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2504741653.518864</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>289717.3843829315</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>365389.2553699138</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>3160975444.949228</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>65798364.71174037</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>69163927.09671135</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>55564987.79166572</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>143304274.9096381</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>2492173890.439473</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>288263.7017479219</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>365622.3533963226</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>3132965856.763483</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>66036889.79569063</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>68511636.85664195</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>57537140.54130431</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>142047513.4988975</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>2463862676.070949</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>284989.0123347323</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>362382.5523512063</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>3135690098.318007</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>58172514.58777651</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>68580742.67377849</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>64115392.71372245</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>171708475.8308767</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>2438142972.511853</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>282014.0766834738</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>362697.6587560904</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>3158628221.90802</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>56272738.44442231</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>66779011.59463846</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>65580982.41636725</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>172162721.2920108</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>2462862768.160581</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>284873.3554149824</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>365350.8558072972</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>3160938286.851979</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>58566269.03657973</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>67350484.43654014</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>54036624.62865652</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>172114598.1401009</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>2473900310.610102</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>286150.0411458234</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>365618.055409451</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>3155218897.513945</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>56833095.32894609</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>67832370.60736808</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>52509971.5607803</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>172130873.8331746</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>2470942586.183676</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>285807.9283441515</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>364956.5075340624</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>3143557067.882524</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>59600146.6740526</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>65636713.56782462</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>67269600.88137993</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>170384756.6215345</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>2445695850.137733</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>282887.6996965538</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>363607.6120209511</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>3107261838.675294</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>53033216.67019523</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>52235071.51040941</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>66054992.5679894</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>164698591.325855</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>2436269966.600845</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>281797.4306382784</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>359409.4310002758</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>3091727459.264127</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>54010279.01999476</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>33795224.55116672</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>67036073.21227839</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>164389729.7446583</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>2437526152.736029</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>281942.73063793</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>357612.6070584962</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>3086730530.053427</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>54249584.98147089</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>39097420.16805863</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>58569838.14097168</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>164299122.520608</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>2435544564.242318</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>281713.5251090825</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>357034.6243915665</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>3065249157.199693</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>52468408.33213839</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>58466283.61865953</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>51725728.12275265</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>161025661.214919</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>2406593075.911223</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>278364.7767615258</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>354549.9261603557</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>3142760207.197514</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>50848328.25455146</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>37960947.35881008</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>44100083.55514738</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>161097957.4296974</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>2513782890.599308</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>290763.1623196909</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>363515.4410806649</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Σ daily charges</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" s="10" t="n">
+        <v>7896525.085159992</v>
+      </c>
+      <c r="O35" s="10" t="n">
+        <v>10071754.2185237</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -85,6 +85,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -662,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T14:48:50+00:00</t>
+          <t>2026-06-08T17:07:20+00:00</t>
         </is>
       </c>
     </row>
@@ -689,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S58"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4225,47 +4226,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
+          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" s="6" t="n">
-        <v>207131500.431691</v>
+        <v>0</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>287780830.420175</v>
+        <v>0</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>80649329.988484</v>
+        <v>0</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-627039.8278228145</v>
+        <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-627039.8278228145</v>
+        <v>0</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>207131500.431691</v>
+        <v>0</v>
       </c>
       <c r="M54" s="7" t="n">
         <v>0</v>
@@ -4277,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>-627039.8278228145</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="6" t="n">
         <v>0</v>
@@ -4287,276 +4280,173 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>120038508.359851</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>387977397.421864</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>267938889.062013</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>-742151.6061946489</v>
-      </c>
-      <c r="I55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>-742151.6061946489</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>120038508.359851</v>
-      </c>
-      <c r="M55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v>-742151.6061946489</v>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>S59</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="n">
-        <v>285387.136685</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>94443.720094</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>-190943.416591</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>-574.4713114756599</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>-574.4713114756599</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>285387.136685</v>
-      </c>
-      <c r="M56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v>-574.4713114756599</v>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>S60</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>avalanche_c</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="n">
-        <v>95656876.179346</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>152857139.195815</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>57200263.016469</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>-387026.4406245563</v>
-      </c>
-      <c r="I57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>-387026.4406245563</v>
-      </c>
-      <c r="K57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="6" t="n">
-        <v>95656876.179346</v>
-      </c>
-      <c r="M57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v>-387026.4406245563</v>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Pricing cat.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Position SoM</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Position EoM</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PSM_CURVE_DEDUCT</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>Spark Savings V2 — spUSDC vault</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
       <c r="E58" s="6" t="n">
-        <v>0</v>
+        <v>207131500.431691</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
-        </is>
+        <v>287780830.420175</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDT vault</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>120038508.359851</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>387977397.421864</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>285387.136685</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>94443.720094</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>avalanche_c</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>95656876.179346</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>152857139.195815</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" s="9" t="n">
+        <v>-1756792.345953495</v>
       </c>
     </row>
   </sheetData>
@@ -4664,14 +4554,14 @@
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days credited to prime_agent_revenue. Sky still charges full BR on the underlying utilized; this row is the prime's offsetting pickup on the share-price-appreciation accounting (SSR + BR + 30 bps nets to zero economically).</t>
         </is>
@@ -4991,7 +4881,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -6463,10 +6353,10 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="10" t="n">
+      <c r="N35" s="11" t="n">
         <v>7896525.085159992</v>
       </c>
-      <c r="O35" s="10" t="n">
+      <c r="O35" s="11" t="n">
         <v>10071754.2185237</v>
       </c>
     </row>

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>114973.4911231597</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>5286406.061654161</v>
+        <v>5401379.55277732</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7664508.347600595</v>
+        <v>7870949.782221217</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>7698759.412285886</v>
+        <v>7905200.846906506</v>
       </c>
     </row>
     <row r="13">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>7664508.347600595</v>
+        <v>7870949.782221217</v>
       </c>
     </row>
     <row r="15">
@@ -574,23 +574,23 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2407245.870923101</v>
+        <v>-2657160.355716398</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>10071754.2185237</v>
+        <v>10528110.13793761</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — credited to prime_agent_revenue</t>
+          <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>141076.1013865625</v>
+        <v>160996.253256423</v>
       </c>
     </row>
     <row r="20">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-7664508.347600595</v>
+        <v>-7870949.782221217</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-2519178.387332997</v>
+        <v>-2745539.973823479</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T17:07:20+00:00</t>
+          <t>2026-06-09T16:57:25+00:00</t>
         </is>
       </c>
     </row>
@@ -860,13 +860,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1597516.094726083</v>
+        <v>1643843.98727655</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1597516.094726083</v>
+        <v>1643843.98727655</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-1597516.094726083</v>
+        <v>-1643843.98727655</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -925,13 +925,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1413416.20608737</v>
+        <v>1454405.210417829</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1413416.20608737</v>
+        <v>1454405.210417829</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1411583.79391263</v>
+        <v>1370594.789582171</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -990,13 +990,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1228569.152807245</v>
+        <v>1264197.601177796</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1228569.152807245</v>
+        <v>1264197.601177796</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>24529.42100002097</v>
+        <v>-11099.02737053005</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>90251565.90411383</v>
@@ -1059,13 +1059,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>629116.5164740883</v>
+        <v>647360.8662325382</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>629116.5164740883</v>
+        <v>647360.8662325382</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>89298.96391294656</v>
+        <v>71054.61415449658</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>69623450.80112581</v>
@@ -1128,13 +1128,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>605600.0147478303</v>
+        <v>623162.387048442</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>605600.0147478303</v>
+        <v>623162.387048442</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-193155.2177458303</v>
+        <v>-210717.5900464421</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1193,13 +1193,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>528435.9418512845</v>
+        <v>543760.5596217795</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>483335.5566696879</v>
+        <v>498660.174440183</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-528435.9418512845</v>
+        <v>-543760.5596217795</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1258,13 +1258,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>460852.656716032</v>
+        <v>474217.3623565086</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>460852.656716032</v>
+        <v>474217.3623565086</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>121561.7794890887</v>
+        <v>108197.0738486122</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1323,13 +1323,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>269246.186608593</v>
+        <v>277054.3135151108</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>269246.186608593</v>
+        <v>277054.3135151108</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-256419.5369196754</v>
+        <v>-264227.6638261932</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1388,13 +1388,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>269229.346395646</v>
+        <v>277036.9849367705</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>269229.346395646</v>
+        <v>277036.9849367705</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-207916.359358646</v>
+        <v>-215723.9978997705</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1453,13 +1453,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>272226.5773132768</v>
+        <v>280121.1354118062</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>248992.874756096</v>
+        <v>256887.4328546254</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-272226.5773132768</v>
+        <v>-280121.1354118062</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1518,13 +1518,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>202148.1620732098</v>
+        <v>208010.4493845673</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>184895.4370952043</v>
+        <v>190757.7244065618</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-202148.1620732098</v>
+        <v>-208010.4493845673</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1583,13 +1583,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>117954.4743135079</v>
+        <v>121375.1485902075</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>117954.4743135079</v>
+        <v>121375.1485902075</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-14145.85352650795</v>
+        <v>-17566.52780320751</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1648,13 +1648,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>89828.26168491939</v>
+        <v>92433.27710171101</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>89828.26168491939</v>
+        <v>92433.27710171101</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>12118.71975629463</v>
+        <v>9513.704339503005</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>-55265.60425743128</v>
+        <v>-75185.75612729185</v>
       </c>
       <c r="P15" s="6" t="n">
         <v>0</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>55265.60425743128</v>
+        <v>75185.75612729185</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1774,13 +1774,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>35330.58255634345</v>
+        <v>36355.16780954952</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>35330.58255634345</v>
+        <v>36355.16780954952</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>23133.57609824207</v>
+        <v>22108.99084503601</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1908,13 +1908,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>26925.27728596954</v>
+        <v>27706.10907671892</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>26925.27728596954</v>
+        <v>27706.10907671892</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-7503.179921969538</v>
+        <v>-8284.011712718922</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1973,13 +1973,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13598.36085890023</v>
+        <v>13992.71269223285</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>13598.36085890023</v>
+        <v>13992.71269223285</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-13598.36085890587</v>
+        <v>-13992.71269223849</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>13493.78296323714</v>
+        <v>13885.10204245265</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>13493.78296323714</v>
+        <v>13885.10204245265</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-13493.78296323501</v>
+        <v>-13885.10204245053</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>13421.03217282908</v>
+        <v>13810.24148250167</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>13421.03217282908</v>
+        <v>13810.24148250167</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-13421.03217282898</v>
+        <v>-13810.24148250157</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2168,13 +2168,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>13236.13148725027</v>
+        <v>13619.97868562878</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>13236.13148725027</v>
+        <v>13619.97868562878</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-13236.13148725277</v>
+        <v>-13619.97868563128</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2233,13 +2233,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>2627.142980808697</v>
+        <v>2703.330005234569</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>2627.142980808697</v>
+        <v>2703.330005234569</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-366.2712630040895</v>
+        <v>-442.4582874299612</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2298,13 +2298,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>2620.884115307928</v>
+        <v>2696.88963292497</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>2397.199702959646</v>
+        <v>2473.205220576689</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-2620.884115307928</v>
+        <v>-2696.88963292497</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2363,13 +2363,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>186.8702200246323</v>
+        <v>192.2894477261647</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>186.8702200246323</v>
+        <v>192.2894477261647</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-186.8702200247224</v>
+        <v>-192.2894477262547</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1.450556012438627</v>
+        <v>1.492622069428314</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.450556012438627</v>
+        <v>1.492622069428314</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-1.450556034276827</v>
+        <v>-1.492622091266514</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2493,13 +2493,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>1.343968904721477</v>
+        <v>1.382943940537802</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.343968904721477</v>
+        <v>1.382943940537802</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-0.1268887708071693</v>
+        <v>-0.1658638066234949</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2558,13 +2558,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.905705179035562</v>
+        <v>0.9319705871621422</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.905705179035562</v>
+        <v>0.9319705871621422</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3565438314977682</v>
+        <v>0.330278423371188</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2623,13 +2623,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.7643827127248842</v>
+        <v>0.7865497758921727</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.7643827127248842</v>
+        <v>0.7865497758921727</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.7643827127248842</v>
+        <v>-0.7865497758921727</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2688,13 +2688,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2654963933229446</v>
+        <v>0.2731957763983376</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2654963933229446</v>
+        <v>0.2731957763983376</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.008545803616848612</v>
+        <v>0.0008464205414555964</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2753,13 +2753,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.0589823983502668</v>
+        <v>0.06069288516298874</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.0589823983502668</v>
+        <v>0.06069288516298874</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.05897214230286214</v>
+        <v>-0.06068262911558407</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.003259452092740379</v>
+        <v>0.003353976052044691</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.003259452092740379</v>
+        <v>0.003353976052044691</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.003249452092740379</v>
+        <v>-0.003343976052044691</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2883,13 +2883,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.0001544234975243615</v>
+        <v>0.0001589017717803731</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.0001544234975243615</v>
+        <v>0.0001589017717803731</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-4.542349752436153e-05</v>
+        <v>-4.99017717803731e-05</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2948,13 +2948,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>1.698943873799075e-05</v>
+        <v>1.748213167231848e-05</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>1.698943873799075e-05</v>
+        <v>1.748213167231848e-05</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-7.989438737990746e-06</v>
+        <v>-8.482131672318483e-06</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3013,13 +3013,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>1.545303844792421e-05</v>
+        <v>1.590117584519808e-05</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>1.545303844792421e-05</v>
+        <v>1.590117584519808e-05</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-1.41265427394882e-05</v>
+        <v>-1.457468013676208e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3078,13 +3078,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>4.544876797104339e-06</v>
+        <v>4.676678013133693e-06</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>4.544876797104339e-06</v>
+        <v>4.676678013133693e-06</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-5.448767971043391e-07</v>
+        <v>-6.766780131336924e-07</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3143,13 +3143,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>3.339043091263772e-06</v>
+        <v>3.43587518582866e-06</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>3.339043091263772e-06</v>
+        <v>3.43587518582866e-06</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-3.339043091263772e-06</v>
+        <v>-3.43587518582866e-06</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3208,13 +3208,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.395834598574509e-06</v>
+        <v>1.436313737103672e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.395834598574509e-06</v>
+        <v>1.436313737103672e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-5.73536139079509e-07</v>
+        <v>-6.140152776086717e-07</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.016554185529916e-07</v>
+        <v>2.075034163251482e-07</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.016554185529916e-07</v>
+        <v>2.075034163251482e-07</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.016554185529916e-07</v>
+        <v>-2.075034163251482e-07</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7664508.347600595</v>
+        <v>7870949.782221217</v>
       </c>
     </row>
     <row r="5">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7698759.412285886</v>
+        <v>7905200.846906506</v>
       </c>
     </row>
     <row r="8">
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10071754.2185237</v>
+        <v>10528110.13793761</v>
       </c>
     </row>
     <row r="11">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>7664508.347600595</v>
+        <v>7870949.782221217</v>
       </c>
     </row>
     <row r="12">
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-2407245.870923101</v>
+        <v>-2657160.355716398</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -4563,11 +4563,11 @@
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days credited to prime_agent_revenue. Sky still charges full BR on the underlying utilized; this row is the prime's offsetting pickup on the share-price-appreciation accounting (SSR + BR + 30 bps nets to zero economically).</t>
+          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>141076.1013865625</v>
+        <v>160996.253256423</v>
       </c>
     </row>
     <row r="17">
@@ -4883,7 +4883,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>
@@ -4970,16 +4970,16 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>3159527983.465951</v>
+        <v>3302687682.017447</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>44911720.79857019</v>
+        <v>105171462.9946192</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>70289118.90880118</v>
+        <v>90273216.51830859</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>53443795.92462372</v>
@@ -4988,7 +4988,7 @@
         <v>222761546.1543027</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2433151801.679653</v>
+        <v>2496067660.425592</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.04</v>
@@ -5006,10 +5006,10 @@
         <v>0.04312</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>281436.7600742012</v>
+        <v>288714.084666329</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>365454.9290416628</v>
+        <v>382013.8637146737</v>
       </c>
     </row>
     <row r="7">
@@ -5019,16 +5019,16 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>3108979150.764832</v>
+        <v>3249848457.938409</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>42264739.63239259</v>
+        <v>105454422.331356</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>70082020.93708614</v>
+        <v>90066118.53740281</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>60874882.1318847</v>
@@ -5037,7 +5037,7 @@
         <v>202280884.9245871</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>2398506623.138882</v>
+        <v>2456202150.013179</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>0.04</v>
@@ -5055,10 +5055,10 @@
         <v>0.04312</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>277429.4364070235</v>
+        <v>284102.9378889561</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>359608.0683192389</v>
+        <v>375902.0789837033</v>
       </c>
     </row>
     <row r="8">
@@ -5068,16 +5068,16 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>3139557721.076495</v>
+        <v>3281812557.64904</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>45903618.77129755</v>
+        <v>105461810.0916423</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>71919290.05995171</v>
+        <v>91903387.66823922</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>56917531.56825144</v>
@@ -5086,7 +5086,7 @@
         <v>205373147.2248062</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>2424474133.452188</v>
+        <v>2487186681.096101</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0.04</v>
@@ -5104,10 +5104,10 @@
         <v>0.04312</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>280433.0352637514</v>
+        <v>287686.8433544418</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>363145.0172881749</v>
+        <v>379599.2887735071</v>
       </c>
     </row>
     <row r="9">
@@ -5117,16 +5117,16 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>3141266002.661607</v>
+        <v>3283598242.276013</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>50573746.36953703</v>
+        <v>105690919.88651</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>72165573.01717961</v>
+        <v>92149670.62473042</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>59127098.93596155</v>
@@ -5135,7 +5135,7 @@
         <v>199490512.222793</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2424939072.116136</v>
+        <v>2492170040.606018</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0.04</v>
@@ -5153,10 +5153,10 @@
         <v>0.04312</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>280486.8135899226</v>
+        <v>288263.2564470355</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>363342.6100706212</v>
+        <v>379805.8345778349</v>
       </c>
     </row>
     <row r="10">
@@ -5166,16 +5166,16 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3053995867.48157</v>
+        <v>3192373856.236259</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>49019765.63915107</v>
+        <v>105396023.5861312</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>71955022.75225696</v>
+        <v>91939120.36032036</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>74193559.24762456</v>
@@ -5184,7 +5184,7 @@
         <v>168645198.529759</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2355212321.312778</v>
+        <v>2417229954.512424</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.04</v>
@@ -5202,10 +5202,10 @@
         <v>0.04312</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>272421.6896535321</v>
+        <v>279595.11867803</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>353248.2854668903</v>
+        <v>369254.1313799236</v>
       </c>
     </row>
     <row r="11">
@@ -5215,16 +5215,16 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>2984358626.829742</v>
+        <v>3119581319.466832</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>43420025.24945795</v>
+        <v>106086355.1901842</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>70093687.03120825</v>
+        <v>90077784.61901149</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>62663404.50552572</v>
@@ -5233,7 +5233,7 @@
         <v>139389471.4291162</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>2333822038.614434</v>
+        <v>2386394303.722994</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.04</v>
@@ -5251,10 +5251,10 @@
         <v>0.04312</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>269947.5275993859</v>
+        <v>276028.4338345421</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>345193.5149523549</v>
+        <v>360834.3954259945</v>
       </c>
     </row>
     <row r="12">
@@ -5264,16 +5264,16 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>2973910687.81137</v>
+        <v>3108659979.418882</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>43331747.98936062</v>
+        <v>106019996.7568064</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>69404974.57314776</v>
+        <v>89389072.16228232</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>56117349.84955318</v>
@@ -5282,7 +5282,7 @@
         <v>137059463.4132225</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>2333027151.986086</v>
+        <v>2385104097.237017</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.04</v>
@@ -5300,10 +5300,10 @@
         <v>0.04312</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>269855.5849934399</v>
+        <v>275879.1987835314</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>343985.0272185631</v>
+        <v>359571.1505447495</v>
       </c>
     </row>
     <row r="13">
@@ -5313,16 +5313,16 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>2973897203.641477</v>
+        <v>3108645884.27491</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>42972324.58983186</v>
+        <v>105747982.6229086</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>69296818.10221891</v>
+        <v>89281333.2514607</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>44993194.46390114</v>
@@ -5331,7 +5331,7 @@
         <v>136750375.5576032</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2344914490.927922</v>
+        <v>2396902998.379037</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0.04</v>
@@ -5349,10 +5349,10 @@
         <v>0.04312</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>271230.5646208453</v>
+        <v>277243.9490254003</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>343983.4675373774</v>
+        <v>359569.5201936759</v>
       </c>
     </row>
     <row r="14">
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>3092551877.583306</v>
+        <v>3232676857.284869</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>42899555.11684096</v>
+        <v>105680758.0916614</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>68988108.87019685</v>
+        <v>88971646.23857105</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>61607865.93892223</v>
@@ -5380,7 +5380,7 @@
         <v>131807128.8914069</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2452279218.765939</v>
+        <v>2509639458.124308</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>0.04</v>
@@ -5398,10 +5398,10 @@
         <v>0.04312</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>283649.1819582925</v>
+        <v>290283.901547492</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>357707.9655234039</v>
+        <v>373915.8816367543</v>
       </c>
     </row>
     <row r="15">
@@ -5411,16 +5411,16 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3109481334.50664</v>
+        <v>3250373395.861687</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>42923510.8116744</v>
+        <v>105677548.8383867</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>69468489.83052413</v>
+        <v>89452806.54322197</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>56661540.26184572</v>
@@ -5429,7 +5429,7 @@
         <v>136841950.8508666</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2468615842.751729</v>
+        <v>2526769549.367366</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>0.04</v>
@@ -5447,10 +5447,10 @@
         <v>0.04312</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>285538.7995817952</v>
+        <v>292265.2976017348</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>359666.1546931178</v>
+        <v>375962.797278495</v>
       </c>
     </row>
     <row r="16">
@@ -5460,16 +5460,16 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>3145504400.532222</v>
+        <v>3288028683.947055</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>66366024.4559039</v>
+        <v>105914703.1651621</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>69840737.56294712</v>
+        <v>89824835.18476696</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>63224001.35398827</v>
@@ -5478,7 +5478,7 @@
         <v>142782678.6256742</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>2468320958.533709</v>
+        <v>2551312465.617463</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>0.04</v>
@@ -5496,10 +5496,10 @@
         <v>0.04312</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>285504.691040413</v>
+        <v>295104.1171227493</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>363832.8552595108</v>
+        <v>380318.2930067479</v>
       </c>
     </row>
     <row r="17">
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>3136818758.084431</v>
+        <v>3278949490.955936</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>65825302.58991265</v>
+        <v>105383666.0382448</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>70258797.83252665</v>
+        <v>90242895.45406024</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>52662079.36682548</v>
@@ -5527,7 +5527,7 @@
         <v>138982244.1528277</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2474120334.142338</v>
+        <v>2556708605.943978</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0.04</v>
@@ -5545,10 +5545,10 @@
         <v>0.04312</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>286175.4907334776</v>
+        <v>295728.2755699747</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>362828.208090361</v>
+        <v>379268.1248019754</v>
       </c>
     </row>
     <row r="18">
@@ -5558,16 +5558,16 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>3148361751.906786</v>
+        <v>3291015503.255936</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>66204220.05029075</v>
+        <v>105598058.7788601</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>69557060.69633225</v>
+        <v>89541166.78652765</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>42287173.46979559</v>
@@ -5576,7 +5576,7 @@
         <v>142368665.4817924</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>2492974632.208575</v>
+        <v>2576250438.738961</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>0.04</v>
@@ -5594,10 +5594,10 @@
         <v>0.04312</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>288356.32160378</v>
+        <v>297988.6319126965</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>364163.3581540263</v>
+        <v>380663.7711428175</v>
       </c>
     </row>
     <row r="19">
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>3118135878.924826</v>
+        <v>3259420081.756857</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>66237408.33460446</v>
+        <v>105631908.5331736</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>69255485.04462956</v>
+        <v>89239582.66275901</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>53265841.76145346</v>
@@ -5625,7 +5625,7 @@
         <v>139402138.7763296</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2455005005.007809</v>
+        <v>2536910610.023141</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>0.04</v>
@@ -5643,10 +5643,10 @@
         <v>0.04312</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>283964.4670334108</v>
+        <v>293438.2894605687</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>360667.2048287037</v>
+        <v>377009.2054664214</v>
       </c>
     </row>
     <row r="20">
@@ -5656,16 +5656,16 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>3087993177.392972</v>
+        <v>3227911600.245395</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>66140189.59027819</v>
+        <v>105536765.3215168</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>69605286.29178502</v>
+        <v>89588813.97299054</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>53138187.3806347</v>
@@ -5674,7 +5674,7 @@
         <v>136407246.0004658</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2427732268.129808</v>
+        <v>2508270587.569788</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>0.04</v>
@@ -5692,10 +5692,10 @@
         <v>0.04312</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>280809.8957896429</v>
+        <v>290125.567614706</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>357180.6717430357</v>
+        <v>373364.6959272624</v>
       </c>
     </row>
     <row r="21">
@@ -5705,16 +5705,16 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>3158960204.002114</v>
+        <v>3302094176.199131</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>65730562.95242047</v>
+        <v>105575697.6945751</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>69323084.617901</v>
+        <v>89307182.23349793</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>47401363.76374279</v>
@@ -5723,7 +5723,7 @@
         <v>136793539.1491862</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2504741653.518864</v>
+        <v>2588046393.35813</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>0.04</v>
@@ -5741,10 +5741,10 @@
         <v>0.04312</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>289717.3843829315</v>
+        <v>299353.0413374227</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>365389.2553699138</v>
+        <v>381945.2143379779</v>
       </c>
     </row>
     <row r="22">
@@ -5754,16 +5754,16 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>3160975444.949228</v>
+        <v>3304200728.661132</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>65798364.71174037</v>
+        <v>105565151.0821526</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>69163927.09671135</v>
+        <v>89147800.24280986</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>55564987.79166572</v>
@@ -5772,7 +5772,7 @@
         <v>143304274.9096381</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>2492173890.439473</v>
+        <v>2575648514.634866</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>0.04</v>
@@ -5790,10 +5790,10 @@
         <v>0.04312</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>288263.7017479219</v>
+        <v>297919.008813328</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>365622.3533963226</v>
+        <v>382188.8741455667</v>
       </c>
     </row>
     <row r="23">
@@ -5803,16 +5803,16 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>3132965856.763483</v>
+        <v>3274922012.864489</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>66036889.79569063</v>
+        <v>105681775.6869586</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>68511636.85664195</v>
+        <v>88495634.47039659</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>57537140.54130431</v>
@@ -5821,7 +5821,7 @@
         <v>142047513.4988975</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2463862676.070949</v>
+        <v>2546189948.666932</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>0.04</v>
@@ -5839,10 +5839,10 @@
         <v>0.04312</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>284989.0123347323</v>
+        <v>294511.6080269389</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>362382.5523512063</v>
+        <v>378802.2761917308</v>
       </c>
     </row>
     <row r="24">
@@ -5852,16 +5852,16 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>3135690098.318007</v>
+        <v>3277769691.084796</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>58172514.58777651</v>
+        <v>105839845.8064453</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>68580742.67377849</v>
+        <v>88579423.51548044</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>64115392.71372245</v>
@@ -5870,7 +5870,7 @@
         <v>171708475.8308767</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2438142972.511853</v>
+        <v>2512556553.218271</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0.04</v>
@@ -5888,10 +5888,10 @@
         <v>0.04312</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>282014.0766834738</v>
+        <v>290621.3148529449</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>362697.6587560904</v>
+        <v>379131.6602159843</v>
       </c>
     </row>
     <row r="25">
@@ -5901,16 +5901,16 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>3158628221.90802</v>
+        <v>3301747151.840255</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>56272738.44442231</v>
+        <v>106244104.3858212</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>66779011.59463846</v>
+        <v>86620267.0626184</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>65580982.41636725</v>
@@ -5919,7 +5919,7 @@
         <v>172162721.2920108</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2462862768.160581</v>
+        <v>2536169076.683437</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0.04</v>
@@ -5937,10 +5937,10 @@
         <v>0.04312</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>284873.3554149824</v>
+        <v>293352.5180999535</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>365350.8558072972</v>
+        <v>381905.0748731234</v>
       </c>
     </row>
     <row r="26">
@@ -5950,16 +5950,16 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>3160938286.851979</v>
+        <v>3304161886.913025</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>58566269.03657973</v>
+        <v>106190262.4644004</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>67350484.43654014</v>
+        <v>87350484.05449657</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>54036624.62865652</v>
@@ -5968,7 +5968,7 @@
         <v>172114598.1401009</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>2473900310.610102</v>
+        <v>2549499917.625371</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0.04</v>
@@ -5986,10 +5986,10 @@
         <v>0.04312</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>286150.0411458234</v>
+        <v>294894.4640982148</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>365618.055409451</v>
+        <v>382184.381414889</v>
       </c>
     </row>
     <row r="27">
@@ -5999,16 +5999,16 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>3155218897.513945</v>
+        <v>3298183349.354809</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>56833095.32894609</v>
+        <v>105749238.4054566</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>67832370.60736808</v>
+        <v>87831880.21825115</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>52509971.5607803</v>
@@ -6017,7 +6017,7 @@
         <v>172130873.8331746</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>2470942586.183676</v>
+        <v>2544991385.337146</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0.04</v>
@@ -6035,10 +6035,10 @@
         <v>0.04312</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>285807.9283441515</v>
+        <v>294372.9731172526</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>364956.5075340624</v>
+        <v>381492.8584942045</v>
       </c>
     </row>
     <row r="28">
@@ -6048,16 +6048,16 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>3143557067.882524</v>
+        <v>3285993116.739357</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>59600146.6740526</v>
+        <v>105650029.128424</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>65636713.56782462</v>
+        <v>85638134.64147896</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>67269600.88137993</v>
@@ -6066,7 +6066,7 @@
         <v>170384756.6215345</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>2445695850.137733</v>
+        <v>2522080595.466539</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0.04</v>
@@ -6084,10 +6084,10 @@
         <v>0.04312</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>282887.6996965538</v>
+        <v>291722.9376909906</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>363607.6120209511</v>
+        <v>380082.8438911389</v>
       </c>
     </row>
     <row r="29">
@@ -6097,16 +6097,16 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>3107261838.675294</v>
+        <v>3248053333.630609</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>53033216.67019523</v>
+        <v>105656287.4630376</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>52235071.51040941</v>
+        <v>72235071.09160909</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>66054992.5679894</v>
@@ -6115,7 +6115,7 @@
         <v>164698591.325855</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>2436269966.600845</v>
+        <v>2504438391.182117</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0.04</v>
@@ -6133,10 +6133,10 @@
         <v>0.04312</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>281797.4306382784</v>
+        <v>289682.3067649023</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>359409.4310002758</v>
+        <v>375694.441314418</v>
       </c>
     </row>
     <row r="30">
@@ -6146,16 +6146,16 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>3091727459.264127</v>
+        <v>3231815084.184004</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>54010279.01999476</v>
+        <v>105835028.346491</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>33795224.55116672</v>
+        <v>53793836.9446341</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>67036073.21227839</v>
@@ -6164,7 +6164,7 @@
         <v>164389729.7446583</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>2437526152.736029</v>
+        <v>2505790415.935942</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>0.04</v>
@@ -6182,10 +6182,10 @@
         <v>0.04312</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>281942.73063793</v>
+        <v>289838.6921848313</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>357612.6070584962</v>
+        <v>373816.2024349638</v>
       </c>
     </row>
     <row r="31">
@@ -6195,16 +6195,16 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>3086730530.053427</v>
+        <v>3226591741.761195</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>54249584.98147089</v>
+        <v>105770621.9190764</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>39097420.16805863</v>
+        <v>59097324.34855221</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>58569838.14097168</v>
@@ -6213,7 +6213,7 @@
         <v>164299122.520608</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>2435544564.242318</v>
+        <v>2503884834.831986</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>0.04</v>
@@ -6231,10 +6231,10 @@
         <v>0.04312</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>281713.5251090825</v>
+        <v>289618.2782461753</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>357034.6243915665</v>
+        <v>373212.0311016261</v>
       </c>
     </row>
     <row r="32">
@@ -6244,16 +6244,16 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>3065249157.199693</v>
+        <v>3204137037.802844</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>52468408.33213839</v>
+        <v>105484587.1280991</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>58466283.61865953</v>
+        <v>78466307.67748198</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>51725728.12275265</v>
@@ -6262,7 +6262,7 @@
         <v>161025661.214919</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>2406593075.911223</v>
+        <v>2472464753.659592</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>0.04</v>
@@ -6280,10 +6280,10 @@
         <v>0.04312</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>278364.7767615258</v>
+        <v>285983.9937595589</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>354549.9261603557</v>
+        <v>370614.7500252457</v>
       </c>
     </row>
     <row r="33">
@@ -6293,16 +6293,16 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>3142760207.197514</v>
+        <v>3285160149.922022</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>334970000</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>50848328.25455146</v>
+        <v>105774524.3487542</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>37960947.35881008</v>
+        <v>57961427.91663297</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>44100083.55514738</v>
@@ -6311,7 +6311,7 @@
         <v>161097957.4296974</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>2513782890.599308</v>
+        <v>2581256156.67179</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>0.04</v>
@@ -6329,10 +6329,10 @@
         <v>0.04312</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>290763.1623196909</v>
+        <v>298567.6311497718</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>363515.4410806649</v>
+        <v>379986.4966422093</v>
       </c>
     </row>
     <row r="35">
@@ -6354,10 +6354,10 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" s="11" t="n">
-        <v>7896525.085159992</v>
+        <v>8122886.671650474</v>
       </c>
       <c r="O35" s="11" t="n">
-        <v>10071754.2185237</v>
+        <v>10528110.13793761</v>
       </c>
     </row>
   </sheetData>

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5286406.061654161</v>
+        <v>7043198.407607656</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>5401379.55277732</v>
+        <v>7158171.898730815</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>5286406.061654161</v>
+        <v>7043198.407607656</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-2745539.973823479</v>
+        <v>-988747.6278699836</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T16:57:25+00:00</t>
+          <t>2026-06-09T22:28:13+00:00</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" s="9" t="n">
-        <v>-1756792.345953495</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T22:28:13+00:00</t>
+          <t>2026-06-09T23:15:52+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7043198.407607656</v>
+        <v>10291414.06300926</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>7158171.898730815</v>
+        <v>10406387.55413242</v>
       </c>
     </row>
     <row r="8">
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>34251.0646852904</v>
+        <v>3733.879168749717</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>7905200.846906506</v>
+        <v>7874683.661389966</v>
       </c>
     </row>
     <row r="13">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7043198.407607656</v>
+        <v>10291414.06300926</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-988747.6278699836</v>
+        <v>1305516.352790914</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T23:15:52+00:00</t>
+          <t>2026-06-10T10:55:08+00:00</t>
         </is>
       </c>
     </row>
@@ -842,13 +842,13 @@
         <v>405093823.4685989</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0</v>
+        <v>1138527.958990891</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0</v>
+        <v>1138527.958990891</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>1643843.98727655</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-1643843.98727655</v>
+        <v>-505316.0282856596</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -1175,13 +1175,13 @@
         <v>591393.88095773</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0</v>
+        <v>591393.88095773</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0</v>
+        <v>591393.88095773</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
@@ -1199,7 +1199,7 @@
         <v>498660.174440183</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-543760.5596217795</v>
+        <v>47633.32133595052</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1435,13 +1435,13 @@
         <v>304659.6934590152</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0</v>
+        <v>304659.6934590152</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0</v>
+        <v>304659.6934590152</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>256887.4328546254</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-280121.1354118062</v>
+        <v>24538.55804720898</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1500,13 +1500,13 @@
         <v>226232.1250862077</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>226232.1250862077</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0</v>
+        <v>226232.1250862077</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>190757.7244065618</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-208010.4493845673</v>
+        <v>18221.6757016404</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1793,128 +1793,124 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>49999911.74966041</v>
+        <v>10000965.036792</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>50000340.64647674</v>
+        <v>10000143.505486</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>428.8968163312471</v>
+        <v>-821.531306</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>34251.0646852904</v>
+        <v>19422.097364</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0</v>
+        <v>19422.097364</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>34251.0646852904</v>
+        <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>49998703.81509366</v>
+        <v>10000242.05005379</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0</v>
+        <v>27706.10907671892</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>34251.0646852904</v>
+        <v>27706.10907671892</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0</v>
+        <v>-8284.011712718922</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>49998703.81509366</v>
+        <v>0</v>
       </c>
       <c r="R17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>10000965.036792</v>
+        <v>4994817.315553</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>10000143.505486</v>
+        <v>4983790.597531</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-821.531306</v>
+        <v>-11026.718022</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>19422.097364</v>
+        <v>-5.6402e-09</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>19422.097364</v>
+        <v>-5.6402e-09</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>10000242.05005379</v>
+        <v>5050529.234246395</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>27706.10907671892</v>
+        <v>13992.71269223285</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>27706.10907671892</v>
+        <v>13992.71269223285</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-8284.011712718922</v>
+        <v>-13992.71269223849</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1927,17 +1923,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1946,40 +1942,40 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>4994817.315553</v>
+        <v>4979093.435761</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>4983790.597531</v>
+        <v>5000000</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-11026.718022</v>
+        <v>20906.564239</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-5.6402e-09</v>
+        <v>2.1207e-09</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-5.6402e-09</v>
+        <v>2.1207e-09</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>5050529.234246395</v>
+        <v>5011688.25004375</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13992.71269223285</v>
+        <v>13885.10204245265</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>13992.71269223285</v>
+        <v>13885.10204245265</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-13992.71269223849</v>
+        <v>-13885.10204245053</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -1992,17 +1988,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2011,40 +2007,40 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>4979093.435761</v>
+        <v>5000000</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>5000000</v>
+        <v>4997665.827264</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>20906.564239</v>
+        <v>-2334.172736</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2.1207e-09</v>
+        <v>1.013e-10</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2.1207e-09</v>
+        <v>1.013e-10</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>5011688.25004375</v>
+        <v>4984668.082129179</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>13885.10204245265</v>
+        <v>13810.24148250167</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>13885.10204245265</v>
+        <v>13810.24148250167</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-13885.10204245053</v>
+        <v>-13810.24148250157</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2057,17 +2053,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2079,37 +2075,37 @@
         <v>5000000</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4997665.827264</v>
+        <v>5000000</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-2334.172736</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.013e-10</v>
+        <v>-2.4963e-09</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.013e-10</v>
+        <v>-2.4963e-09</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4984668.082129179</v>
+        <v>4915994.634819037</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>13810.24148250167</v>
+        <v>13619.97868562878</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>13810.24148250167</v>
+        <v>13619.97868562878</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-13810.24148250157</v>
+        <v>-13619.97868563128</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2122,67 +2118,71 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>5000000</v>
+        <v>49999911.74966041</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>5000000</v>
+        <v>50000340.64647674</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0</v>
+        <v>428.8968163312471</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-2.4963e-09</v>
+        <v>3733.879168749717</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0</v>
+        <v>30517.18551654069</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-2.4963e-09</v>
+        <v>30517.18551654069</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0</v>
+        <v>3733.879168749717</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4915994.634819037</v>
+        <v>49998703.81509366</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>13619.97868562878</v>
+        <v>0</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>13619.97868562878</v>
+        <v>3733.879168749717</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-13619.97868563128</v>
+        <v>30517.18551654069</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>0</v>
+        <v>49998703.81509366</v>
       </c>
       <c r="R22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2280,13 +2280,13 @@
         <v>2933.13665051312</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0</v>
+        <v>2933.13665051312</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0</v>
+        <v>2933.13665051312</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
@@ -2304,7 +2304,7 @@
         <v>2473.205220576689</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-2696.88963292497</v>
+        <v>236.2470175881498</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>34251.0646852904</v>
+        <v>3733.879168749717</v>
       </c>
     </row>
     <row r="6">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7905200.846906506</v>
+        <v>7874683.661389966</v>
       </c>
     </row>
     <row r="8">
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>34251.0646852904</v>
+        <v>3733.879168749717</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>34251.0646852904</v>
+        <v>3733.879168749717</v>
       </c>
     </row>
   </sheetData>

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -20,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;&quot;−$&quot;#,##0.00;&quot;$&quot;0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;&quot;−$&quot;#,##0;&quot;$&quot;0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -75,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -86,10 +87,12 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10291414.06300926</v>
+        <v>10291414.08057346</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +501,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>114973.4911231597</v>
+        <v>114973.4961946769</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>10406387.55413242</v>
+        <v>10406387.57676814</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +529,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7870949.782221217</v>
+        <v>7395825.536663454</v>
       </c>
     </row>
     <row r="10">
@@ -536,13 +539,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3733.879168749717</v>
+        <v>3733.877754048192</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>7874683.661389966</v>
+        <v>7399559.414417502</v>
       </c>
     </row>
     <row r="13">
@@ -564,7 +567,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>7870949.782221217</v>
+        <v>7395825.536663454</v>
       </c>
     </row>
     <row r="15">
@@ -574,13 +577,13 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2657160.355716398</v>
+        <v>-2657160.459304557</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>10528110.13793761</v>
+        <v>10052985.99596801</v>
       </c>
     </row>
     <row r="18">
@@ -612,7 +615,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>10291414.06300926</v>
+        <v>10291414.08057346</v>
       </c>
     </row>
     <row r="22">
@@ -622,13 +625,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-7870949.782221217</v>
+        <v>-7395825.536663454</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>1305516.352790914</v>
+        <v>1780640.571690028</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-10T10:55:08+00:00</t>
+          <t>2026-06-23T21:43:40+00:00</t>
         </is>
       </c>
     </row>
@@ -842,13 +845,13 @@
         <v>405093823.4685989</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1138527.958990891</v>
+        <v>1138527.930917541</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1138527.958990891</v>
+        <v>1138527.930917541</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -860,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1643843.98727655</v>
+        <v>1546603.526394521</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1643843.98727655</v>
+        <v>1546603.526394521</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-505316.0282856596</v>
+        <v>-408075.5954769801</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -925,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1454405.210417829</v>
+        <v>1368370.870136812</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1454405.210417829</v>
+        <v>1368370.870136812</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1370594.789582171</v>
+        <v>1456629.129863188</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -990,13 +993,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1264197.601177796</v>
+        <v>1189414.861248716</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1264197.601177796</v>
+        <v>1189414.861248716</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-11099.02737053005</v>
+        <v>63683.71255855043</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>90251565.90411383</v>
@@ -1059,13 +1062,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>647360.8662325382</v>
+        <v>609066.6792679139</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>647360.8662325382</v>
+        <v>609066.6792679139</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>71054.61415449658</v>
+        <v>109348.801119121</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>69623450.80112581</v>
@@ -1128,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>623162.387048442</v>
+        <v>586299.6444828718</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>623162.387048442</v>
+        <v>586299.6444828718</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-210717.5900464421</v>
+        <v>-173854.8474808717</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1193,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>543760.5596217795</v>
+        <v>511594.7775668206</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>498660.174440183</v>
+        <v>466494.3923852241</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>47633.32133595052</v>
+        <v>79799.10339090938</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1258,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>474217.3623565086</v>
+        <v>446165.3603230276</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>474217.3623565086</v>
+        <v>446165.3603230276</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>108197.0738486122</v>
+        <v>136249.0758820931</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1323,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>277054.3135151108</v>
+        <v>260665.3560811403</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>277054.3135151108</v>
+        <v>260665.3560811403</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-264227.6638261932</v>
+        <v>-247838.7063922228</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1388,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>277036.9849367705</v>
+        <v>260649.0525629379</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>277036.9849367705</v>
+        <v>260649.0525629379</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-215723.9978997705</v>
+        <v>-199336.0655259379</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1453,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>280121.1354118062</v>
+        <v>263550.7622370562</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>256887.4328546254</v>
+        <v>240317.0596798754</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>24538.55804720898</v>
+        <v>41108.93122195897</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1518,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>208010.4493845673</v>
+        <v>195705.7342637944</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>190757.7244065618</v>
+        <v>178453.0092857888</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>18221.6757016404</v>
+        <v>30526.3908224133</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1583,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>121375.1485902075</v>
+        <v>114195.2851239119</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>121375.1485902075</v>
+        <v>114195.2851239119</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-17566.52780320751</v>
+        <v>-10386.66433691191</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1648,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>92433.27710171101</v>
+        <v>86965.45014503122</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>92433.27710171101</v>
+        <v>86965.45014503122</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>9513.704339503005</v>
+        <v>14981.5312961828</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1774,13 +1777,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>36355.16780954952</v>
+        <v>34204.60285289504</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>36355.16780954952</v>
+        <v>34204.60285289504</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>22108.99084503601</v>
+        <v>24259.55580169048</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1839,13 +1842,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>27706.10907671892</v>
+        <v>26067.17324295316</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>27706.10907671892</v>
+        <v>26067.17324295316</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-8284.011712718922</v>
+        <v>-6645.075878953161</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1904,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>13992.71269223285</v>
+        <v>13164.98339327619</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>13992.71269223285</v>
+        <v>13164.98339327619</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-13992.71269223849</v>
+        <v>-13164.98339328183</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1969,13 +1972,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13885.10204245265</v>
+        <v>13063.73837749863</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>13885.10204245265</v>
+        <v>13063.73837749863</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-13885.10204245053</v>
+        <v>-13063.73837749651</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2034,13 +2037,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>13810.24148250167</v>
+        <v>12993.30614250297</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>13810.24148250167</v>
+        <v>12993.30614250297</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-13810.24148250157</v>
+        <v>-12993.30614250287</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2099,13 +2102,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>13619.97868562878</v>
+        <v>12814.2982105685</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>13619.97868562878</v>
+        <v>12814.2982105685</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-13619.97868563128</v>
+        <v>-12814.298210571</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2146,16 +2149,16 @@
         <v>428.8968163312471</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>3733.879168749717</v>
+        <v>3733.877754048192</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>30517.18551654069</v>
+        <v>30517.18693124221</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>30517.18551654069</v>
+        <v>30517.18693124221</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>3733.879168749717</v>
+        <v>3733.877754048192</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>49998703.81509366</v>
@@ -2167,10 +2170,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>3733.879168749717</v>
+        <v>3733.877754048192</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>30517.18551654069</v>
+        <v>30517.18693124221</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>49998703.81509366</v>
@@ -2233,13 +2236,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>2703.330005234569</v>
+        <v>2543.41637738431</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>2703.330005234569</v>
+        <v>2543.41637738431</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-442.4582874299612</v>
+        <v>-282.544659579702</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2298,13 +2301,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>2696.88963292497</v>
+        <v>2537.356980870763</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>2473.205220576689</v>
+        <v>2313.672568522481</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>236.2470175881498</v>
+        <v>395.7796696423575</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2363,13 +2366,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>192.2894477261647</v>
+        <v>180.9146976498988</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>192.2894477261647</v>
+        <v>180.9146976498988</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-192.2894477262547</v>
+        <v>-180.9146976499888</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2428,13 +2431,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1.492622069428314</v>
+        <v>1.404327037127612</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.492622069428314</v>
+        <v>1.404327037127612</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-1.492622091266514</v>
+        <v>-1.404327058965812</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2493,13 +2496,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>1.382943940537802</v>
+        <v>1.301136842545064</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.382943940537802</v>
+        <v>1.301136842545064</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-0.1658638066234949</v>
+        <v>-0.08405670863075694</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2558,13 +2561,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.9319705871621422</v>
+        <v>0.8768405078324814</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.9319705871621422</v>
+        <v>0.8768405078324814</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.330278423371188</v>
+        <v>0.3854085027008489</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2623,13 +2626,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.7865497758921727</v>
+        <v>0.7400219646726128</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.7865497758921727</v>
+        <v>0.7400219646726128</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.7865497758921727</v>
+        <v>-0.7400219646726128</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2688,13 +2691,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2731957763983376</v>
+        <v>0.2570350680746657</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2731957763983376</v>
+        <v>0.2570350680746657</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.0008464205414555964</v>
+        <v>0.01700712886512754</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2753,13 +2756,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.06069288516298874</v>
+        <v>0.05710263926910256</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.06069288516298874</v>
+        <v>0.05710263926910256</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.06068262911558407</v>
+        <v>-0.0570923832216979</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2818,13 +2821,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.003353976052044691</v>
+        <v>0.003155573904631387</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.003353976052044691</v>
+        <v>0.003155573904631387</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.003343976052044691</v>
+        <v>-0.003145573904631387</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2883,13 +2886,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.0001589017717803731</v>
+        <v>0.0001495020467197886</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.0001589017717803731</v>
+        <v>0.0001495020467197886</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-4.99017717803731e-05</v>
+        <v>-4.05020467197886e-05</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2948,13 +2951,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>1.748213167231848e-05</v>
+        <v>1.644798819266077e-05</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>1.748213167231848e-05</v>
+        <v>1.644798819266077e-05</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-8.482131672318483e-06</v>
+        <v>-7.447988192660775e-06</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3013,13 +3016,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>1.590117584519808e-05</v>
+        <v>1.49605527205456e-05</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>1.590117584519808e-05</v>
+        <v>1.49605527205456e-05</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-1.457468013676208e-05</v>
+        <v>-1.36340570121096e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3078,13 +3081,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>4.676678013133693e-06</v>
+        <v>4.400032340604024e-06</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>4.676678013133693e-06</v>
+        <v>4.400032340604024e-06</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-6.766780131336924e-07</v>
+        <v>-4.000323406040233e-07</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3143,13 +3146,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>3.43587518582866e-06</v>
+        <v>3.232628351464142e-06</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>3.43587518582866e-06</v>
+        <v>3.232628351464142e-06</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-3.43587518582866e-06</v>
+        <v>-3.232628351464142e-06</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3208,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.436313737103672e-06</v>
+        <v>1.351349585488197e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.436313737103672e-06</v>
+        <v>1.351349585488197e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-6.140152776086717e-07</v>
+        <v>-5.290511259931972e-07</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3273,13 +3276,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.075034163251482e-07</v>
+        <v>1.952286943964069e-07</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.075034163251482e-07</v>
+        <v>1.952286943964069e-07</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.075034163251482e-07</v>
+        <v>-1.952286943964069e-07</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -4460,7 +4463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -4475,195 +4478,377 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Rates &amp; subsidy — effective rate charged this period</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>7870949.782221217</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>3733.879168749717</v>
+          <t>Time-weighted utilized</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>2508076304.951767</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>equals sky_revenue (total Sky take this month)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>7874683.661389966</v>
+          <t xml:space="preserve">  — first $1B (subsidised tranche)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — excess (full base-rate tranche)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1508076304.951767</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base rate (BR = SSR + 30bps), period avg</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>0.04312000189646037</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reference rate (effr), period avg</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>0.0364</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>10528110.13793761</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Subsidised rate (BR*), period avg</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>0.03668000007901918</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>7870949.782221217</v>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Effective blended rate charged</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>0.04055229619917895</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-2657160.355716398</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Diff vs base rate (bps)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>-25.6770569728142</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Subsidy benefit to prime (USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>475124.5953942272</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CoF at full base rate (no subsidy)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>160996.253256423</v>
+        <v>8122887.021486939</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − actual CoF (subsidy on first tranche)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>7647762.426092711</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Subsidy</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = subsidy benefit</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>475124.5953942272</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cap_usd</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>1000000000</v>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Avg balance</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CoF (USD)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>program_start</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+          <t>Subsidised (first $1B)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2763567.547045653</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Excess (&gt; cap)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>1508076304.951767</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>4884194.879047058</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>7395825.536663454</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>3733.877754048192</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equals sky_revenue (total Sky take this month)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>7399559.414417502</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>10052985.99596801</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>7395825.536663454</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-2657160.459304557</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>160996.253256423</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Subsidy</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cap_usd</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>program_start</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>ramp_months</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B41" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>ref_rate_kind</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>effr</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>T this period</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>1 (SoM) → 1 (EoM)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>subsidised_apy = ref_rate + (base_apy − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apy</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
         </is>
@@ -4836,10 +5021,10 @@
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>3733.879168749717</v>
+        <v>3733.877754048192</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>3733.879168749717</v>
+        <v>3733.877754048192</v>
       </c>
     </row>
   </sheetData>
@@ -4881,7 +5066,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -4991,25 +5176,25 @@
         <v>2496067660.425592</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>288714.084666329</v>
+        <v>271745.3615508727</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>382013.8637146737</v>
+        <v>365045.1446174522</v>
       </c>
     </row>
     <row r="7">
@@ -5040,25 +5225,25 @@
         <v>2456202150.013179</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>284102.9378889561</v>
+        <v>267134.214574907</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>375902.0789837033</v>
+        <v>358933.3596232593</v>
       </c>
     </row>
     <row r="8">
@@ -5089,25 +5274,25 @@
         <v>2487186681.096101</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>287686.8433544418</v>
+        <v>270718.1201947443</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>379599.2887735071</v>
+        <v>362630.5695722945</v>
       </c>
     </row>
     <row r="9">
@@ -5138,25 +5323,25 @@
         <v>2492170040.606018</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>288263.2564470355</v>
+        <v>271294.5333121629</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>379805.8345778349</v>
+        <v>362837.1153855179</v>
       </c>
     </row>
     <row r="10">
@@ -5187,25 +5372,25 @@
         <v>2417229954.512424</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>279595.11867803</v>
+        <v>262626.3951698382</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>369254.1313799236</v>
+        <v>352285.4117331658</v>
       </c>
     </row>
     <row r="11">
@@ -5236,25 +5421,25 @@
         <v>2386394303.722994</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>276028.4338345421</v>
+        <v>259059.7101727402</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>360834.3954259945</v>
+        <v>343865.6754166156</v>
       </c>
     </row>
     <row r="12">
@@ -5285,25 +5470,25 @@
         <v>2385104097.237017</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>275879.1987835314</v>
+        <v>258910.4751153023</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>359571.1505447495</v>
+        <v>342602.4304809652</v>
       </c>
     </row>
     <row r="13">
@@ -5334,25 +5519,25 @@
         <v>2396902998.379037</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>277243.9490254003</v>
+        <v>260275.2254159482</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>359569.5201936759</v>
+        <v>342600.8001298214</v>
       </c>
     </row>
     <row r="14">
@@ -5383,25 +5568,25 @@
         <v>2509639458.124308</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>290283.901547492</v>
+        <v>273315.1784996446</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>373915.8816367543</v>
+        <v>356947.1621907688</v>
       </c>
     </row>
     <row r="15">
@@ -5432,25 +5617,25 @@
         <v>2526769549.367366</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>292265.2976017348</v>
+        <v>275296.5746392221</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>375962.797278495</v>
+        <v>358994.0779206661</v>
       </c>
     </row>
     <row r="16">
@@ -5481,25 +5666,25 @@
         <v>2551312465.617463</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>295104.1171227493</v>
+        <v>278135.3942824989</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>380318.2930067479</v>
+        <v>363349.5738365015</v>
       </c>
     </row>
     <row r="17">
@@ -5530,25 +5715,25 @@
         <v>2556708605.943978</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>295728.2755699747</v>
+        <v>278759.5527566056</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>379268.1248019754</v>
+        <v>362299.4055865003</v>
       </c>
     </row>
     <row r="18">
@@ -5579,25 +5764,25 @@
         <v>2576250438.738961</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>297988.6319126965</v>
+        <v>281019.9091966764</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>380663.7711428175</v>
+        <v>363695.0519874501</v>
       </c>
     </row>
     <row r="19">
@@ -5628,25 +5813,25 @@
         <v>2536910610.023141</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>293438.2894605687</v>
+        <v>276469.5665485744</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>377009.2054664214</v>
+        <v>360040.4861536592</v>
       </c>
     </row>
     <row r="20">
@@ -5677,25 +5862,25 @@
         <v>2508270587.569788</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>290125.567614706</v>
+        <v>273156.8445600395</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>373364.6959272624</v>
+        <v>356395.9764575384</v>
       </c>
     </row>
     <row r="21">
@@ -5726,25 +5911,25 @@
         <v>2588046393.35813</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>299353.0413374227</v>
+        <v>282384.3186801649</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>381945.2143379779</v>
+        <v>364976.4952377997</v>
       </c>
     </row>
     <row r="22">
@@ -5775,25 +5960,25 @@
         <v>2575648514.634866</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>297919.008813328</v>
+        <v>280950.2860943094</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>382188.8741455667</v>
+        <v>365220.1550558825</v>
       </c>
     </row>
     <row r="23">
@@ -5824,25 +6009,25 @@
         <v>2546189948.666932</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>294511.6080269389</v>
+        <v>277542.8851611703</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>378802.2761917308</v>
+        <v>361833.5569561925</v>
       </c>
     </row>
     <row r="24">
@@ -5873,25 +6058,25 @@
         <v>2512556553.218271</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>290621.3148529449</v>
+        <v>273652.5918196291</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>379131.6602159843</v>
+        <v>362162.940994632</v>
       </c>
     </row>
     <row r="25">
@@ -5922,25 +6107,25 @@
         <v>2536169076.683437</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>293352.5180999535</v>
+        <v>276383.7951842653</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>381905.0748731234</v>
+        <v>364936.3557712165</v>
       </c>
     </row>
     <row r="26">
@@ -5971,25 +6156,25 @@
         <v>2549499917.625371</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>294894.4640982148</v>
+        <v>277925.7412489351</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>382184.381414889</v>
+        <v>365215.6623250113</v>
       </c>
     </row>
     <row r="27">
@@ -6020,25 +6205,25 @@
         <v>2544991385.337146</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>294372.9731172526</v>
+        <v>277404.2502455133</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>381492.8584942045</v>
+        <v>364524.1393745443</v>
       </c>
     </row>
     <row r="28">
@@ -6069,25 +6254,25 @@
         <v>2522080595.466539</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>291722.9376909906</v>
+        <v>274754.2147051196</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>380082.8438911389</v>
+        <v>363114.1247107522</v>
       </c>
     </row>
     <row r="29">
@@ -6118,25 +6303,25 @@
         <v>2504438391.182117</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>289682.3067649023</v>
+        <v>272713.5836911454</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>375694.441314418</v>
+        <v>358725.7219450316</v>
       </c>
     </row>
     <row r="30">
@@ -6167,25 +6352,25 @@
         <v>2505790415.935942</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>289838.6921848313</v>
+        <v>272869.9691178096</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>373816.2024349638</v>
+        <v>356847.4829846853</v>
       </c>
     </row>
     <row r="31">
@@ -6216,25 +6401,25 @@
         <v>2503884834.831986</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>289618.2782461753</v>
+        <v>272649.5551696609</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>373212.0311016261</v>
+        <v>356243.3116253272</v>
       </c>
     </row>
     <row r="32">
@@ -6265,25 +6450,25 @@
         <v>2472464753.659592</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>285983.9937595589</v>
+        <v>269015.2705265231</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>370614.7500252457</v>
+        <v>353646.0304370871</v>
       </c>
     </row>
     <row r="33">
@@ -6314,25 +6499,25 @@
         <v>2581256156.67179</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.04312</v>
+        <v>0.03668000007901918</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>298567.6311497718</v>
+        <v>281598.908458688</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>379986.4966422093</v>
+        <v>363017.777457673</v>
       </c>
     </row>
     <row r="35">
@@ -6353,11 +6538,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="11" t="n">
-        <v>8122886.671650474</v>
-      </c>
-      <c r="O35" s="11" t="n">
-        <v>10528110.13793761</v>
+      <c r="N35" s="12" t="n">
+        <v>7647762.426092711</v>
+      </c>
+      <c r="O35" s="12" t="n">
+        <v>10052985.99596801</v>
       </c>
     </row>
   </sheetData>

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7395825.536663454</v>
+        <v>7486766.172836288</v>
       </c>
     </row>
     <row r="10">
@@ -545,7 +545,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>7399559.414417502</v>
+        <v>7490500.050590336</v>
       </c>
     </row>
     <row r="13">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>7395825.536663454</v>
+        <v>7486766.172836288</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2657160.459304557</v>
+        <v>-2566219.823131723</v>
       </c>
     </row>
     <row r="16">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-7395825.536663454</v>
+        <v>-7486766.172836288</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>1780640.571690028</v>
+        <v>1689699.935517194</v>
       </c>
     </row>
     <row r="25">
@@ -666,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-23T21:43:40+00:00</t>
+          <t>2026-06-25T11:42:11+00:00</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread + agent rate)</t>
+          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -863,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1546603.526394521</v>
+        <v>1565215.730374914</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1546603.526394521</v>
+        <v>1565215.730374914</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-408075.5954769801</v>
+        <v>-426687.799457373</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -928,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1368370.870136812</v>
+        <v>1384838.178869249</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1368370.870136812</v>
+        <v>1384838.178869249</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1456629.129863188</v>
+        <v>1440161.821130751</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1189414.861248716</v>
+        <v>1203728.569731251</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1189414.861248716</v>
+        <v>1203728.569731251</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>63683.71255855043</v>
+        <v>49370.00407601542</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>90251565.90411383</v>
@@ -1062,13 +1062,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>609066.6792679139</v>
+        <v>616396.3362089024</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>609066.6792679139</v>
+        <v>616396.3362089024</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109348.801119121</v>
+        <v>102019.1441781324</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>69623450.80112581</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>586299.6444828718</v>
+        <v>593355.3173754496</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>586299.6444828718</v>
+        <v>593355.3173754496</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-173854.8474808717</v>
+        <v>-180910.5203734495</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>511594.7775668206</v>
+        <v>517751.4338739319</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>466494.3923852241</v>
+        <v>472651.0486923354</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>79799.10339090938</v>
+        <v>73642.44708379809</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>446165.3603230276</v>
+        <v>451534.6230678736</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>446165.3603230276</v>
+        <v>451534.6230678736</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>136249.0758820931</v>
+        <v>130879.8131372471</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>260665.3560811403</v>
+        <v>263802.2665402248</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>260665.3560811403</v>
+        <v>263802.2665402248</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-247838.7063922228</v>
+        <v>-250975.6168513072</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>260649.0525629379</v>
+        <v>263785.7668215087</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>260649.0525629379</v>
+        <v>263785.7668215087</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-199336.0655259379</v>
+        <v>-202472.7797845087</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>263550.7622370562</v>
+        <v>266722.3963774357</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>240317.0596798754</v>
+        <v>243488.6938202549</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>41108.93122195897</v>
+        <v>37937.29708157951</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1521,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>195705.7342637944</v>
+        <v>198060.9047933366</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>178453.0092857888</v>
+        <v>180808.179815331</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>30526.3908224133</v>
+        <v>28171.22029287117</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1586,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>114195.2851239119</v>
+        <v>115569.539031945</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>114195.2851239119</v>
+        <v>115569.539031945</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-10386.66433691191</v>
+        <v>-11760.91824494497</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1651,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>86965.45014503122</v>
+        <v>88012.01357885409</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>86965.45014503122</v>
+        <v>88012.01357885409</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>14981.5312961828</v>
+        <v>13934.96786235993</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1777,13 +1777,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>34204.60285289504</v>
+        <v>34616.22938451851</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>34204.60285289504</v>
+        <v>34616.22938451851</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>24259.55580169048</v>
+        <v>23847.92927006701</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1842,13 +1842,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>26067.17324295316</v>
+        <v>26380.87196231475</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>26067.17324295316</v>
+        <v>26380.87196231475</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-6645.075878953161</v>
+        <v>-6958.774598314753</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1907,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>13164.98339327619</v>
+        <v>13323.41401375031</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>13164.98339327619</v>
+        <v>13323.41401375031</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-13164.98339328183</v>
+        <v>-13323.41401375595</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1972,13 +1972,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13063.73837749863</v>
+        <v>13220.95059076399</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>13063.73837749863</v>
+        <v>13220.95059076399</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-13063.73837749651</v>
+        <v>-13220.95059076186</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2037,13 +2037,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>12993.30614250297</v>
+        <v>13149.67075707729</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>12993.30614250297</v>
+        <v>13149.67075707729</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-12993.30614250287</v>
+        <v>-13149.67075707719</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>12814.2982105685</v>
+        <v>12968.50860003831</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>12814.2982105685</v>
+        <v>12968.50860003831</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-12814.298210571</v>
+        <v>-12968.50860004081</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2236,13 +2236,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>2543.41637738431</v>
+        <v>2574.024470289222</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>2543.41637738431</v>
+        <v>2574.024470289222</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-282.544659579702</v>
+        <v>-313.1527524846144</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2301,13 +2301,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>2537.356980870763</v>
+        <v>2567.892153520429</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>2313.672568522481</v>
+        <v>2344.207741172148</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>395.7796696423575</v>
+        <v>365.2444969926905</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2366,13 +2366,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>180.9146976498988</v>
+        <v>183.0918692379921</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>180.9146976498988</v>
+        <v>183.0918692379921</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-180.9146976499888</v>
+        <v>-183.0918692380821</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2431,13 +2431,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1.404327037127612</v>
+        <v>1.421227051141632</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.404327037127612</v>
+        <v>1.421227051141632</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-1.404327058965812</v>
+        <v>-1.421227072979832</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2496,13 +2496,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>1.301136842545064</v>
+        <v>1.316795040594249</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.301136842545064</v>
+        <v>1.316795040594249</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-0.08405670863075694</v>
+        <v>-0.09971490667994179</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2561,13 +2561,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.8768405078324814</v>
+        <v>0.8873926203238416</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.8768405078324814</v>
+        <v>0.8873926203238416</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3854085027008489</v>
+        <v>0.3748563902094886</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2626,13 +2626,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.7400219646726128</v>
+        <v>0.7489275694519881</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.7400219646726128</v>
+        <v>0.7489275694519881</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.7400219646726128</v>
+        <v>-0.7489275694519881</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2691,13 +2691,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2570350680746657</v>
+        <v>0.260128290762624</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2570350680746657</v>
+        <v>0.260128290762624</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.01700712886512754</v>
+        <v>0.01391390617716923</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2756,13 +2756,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.05710263926910256</v>
+        <v>0.05778982635471135</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.05710263926910256</v>
+        <v>0.05778982635471135</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.0570923832216979</v>
+        <v>-0.05777957030730669</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2821,13 +2821,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.003155573904631387</v>
+        <v>0.003193548850495581</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.003155573904631387</v>
+        <v>0.003193548850495581</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.003145573904631387</v>
+        <v>-0.003183548850495582</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2886,13 +2886,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.0001495020467197886</v>
+        <v>0.0001513011908065228</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.0001495020467197886</v>
+        <v>0.0001513011908065228</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-4.05020467197886e-05</v>
+        <v>-4.230119080652278e-05</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2951,13 +2951,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>1.644798819266077e-05</v>
+        <v>1.664592729346094e-05</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>1.644798819266077e-05</v>
+        <v>1.664592729346094e-05</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-7.447988192660775e-06</v>
+        <v>-7.645927293460939e-06</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3016,13 +3016,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>1.49605527205456e-05</v>
+        <v>1.514059166015887e-05</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>1.49605527205456e-05</v>
+        <v>1.514059166015887e-05</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-1.36340570121096e-05</v>
+        <v>-1.381409595172287e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3081,13 +3081,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>4.400032340604024e-06</v>
+        <v>4.452983402751516e-06</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>4.400032340604024e-06</v>
+        <v>4.452983402751516e-06</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-4.000323406040233e-07</v>
+        <v>-4.52983402751516e-07</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>3.232628351464142e-06</v>
+        <v>3.271530589331472e-06</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>3.232628351464142e-06</v>
+        <v>3.271530589331472e-06</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-3.232628351464142e-06</v>
+        <v>-3.271530589331472e-06</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3211,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.351349585488197e-06</v>
+        <v>1.367612055930483e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.351349585488197e-06</v>
+        <v>1.367612055930483e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-5.290511259931972e-07</v>
+        <v>-5.453135964354829e-07</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3276,13 +3276,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.952286943964069e-07</v>
+        <v>1.975781241118573e-07</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.952286943964069e-07</v>
+        <v>1.975781241118573e-07</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-1.952286943964069e-07</v>
+        <v>-1.975781241118573e-07</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>7395825.536663454</v>
+        <v>7486766.172836288</v>
       </c>
     </row>
     <row r="25">
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>7399559.414417502</v>
+        <v>7490500.050590336</v>
       </c>
     </row>
     <row r="28">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>7395825.536663454</v>
+        <v>7486766.172836288</v>
       </c>
     </row>
     <row r="32">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2657160.459304557</v>
+        <v>-2566219.823131723</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -505,178 +505,188 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>10406387.57676814</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1014600.24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>11420987.81676814</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>7486766.172836288</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>7486766.172836288</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>3733.877754048192</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
         <v>7490500.050590336</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>7486766.172836288</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>7486766.172836288</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>-2566219.823131723</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
         <v>10052985.99596801</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B19" s="3" t="n">
         <v>160996.253256423</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>10291414.08057346</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>10291414.08057346</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B23" s="3" t="n">
         <v>-7486766.172836288</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" s="4" t="n">
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" s="4" t="n">
         <v>1689699.935517194</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-02-01 → 2026-02-28 (28 days)</t>
-        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>arbitrum=437025050, avalanche_c=79250451, base=42766926, ethereum=24558867, optimism=148362211, unichain=41574840</t>
+          <t>2026-02-01 → 2026-02-28 (28 days)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-25T11:42:11+00:00</t>
+          <t>arbitrum=437025050, avalanche_c=79250451, base=42766926, ethereum=24558867, optimism=148362211, unichain=41574840</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:32:25+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1014600.24</v>
+        <v>1022253.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11420987.81676814</v>
+        <v>11428640.93676814</v>
       </c>
     </row>
     <row r="9">

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10291414.08057346</v>
+        <v>10291414.08057339</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11428640.93676814</v>
+        <v>11428640.93676807</v>
       </c>
     </row>
     <row r="9">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>7486766.172836288</v>
+        <v>7486257.239294591</v>
       </c>
     </row>
     <row r="11">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3733.877754048192</v>
+        <v>3731.279390607106</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>7490500.050590336</v>
+        <v>7489988.518685198</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>7486766.172836288</v>
+        <v>7486257.239294591</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-2566219.823131723</v>
+        <v>-2566728.75667342</v>
       </c>
     </row>
     <row r="17">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>10291414.08057346</v>
+        <v>10291414.08057339</v>
       </c>
     </row>
     <row r="23">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-7486766.172836288</v>
+        <v>-7486257.239294591</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1689699.935517194</v>
+        <v>1690208.869058825</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-25T22:32:25+00:00</t>
+          <t>2026-07-07T00:03:19+00:00</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:S64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -855,13 +855,13 @@
         <v>405093823.4685989</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1138527.930917541</v>
+        <v>1138527.930917483</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1138527.930917541</v>
+        <v>1138527.930917483</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1565215.730374914</v>
+        <v>1565111.570394413</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1565215.730374914</v>
+        <v>1565111.570394413</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-426687.799457373</v>
+        <v>-426583.6394769294</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1384838.178869249</v>
+        <v>1384746.022424032</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1384838.178869249</v>
+        <v>1384746.022424032</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1440161.821130751</v>
+        <v>1440253.977575968</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1203728.569731251</v>
+        <v>1203648.465537357</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1203728.569731251</v>
+        <v>1203648.465537357</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>49370.00407601542</v>
+        <v>49450.1082699095</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>90251565.90411383</v>
@@ -1072,13 +1072,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>616396.3362089024</v>
+        <v>616355.3170515335</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>616396.3362089024</v>
+        <v>616355.3170515335</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>102019.1441781324</v>
+        <v>102060.1633355013</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>69623450.80112581</v>
@@ -1141,13 +1141,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>593355.3173754496</v>
+        <v>593315.8315224206</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>593355.3173754496</v>
+        <v>593315.8315224206</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-180910.5203734495</v>
+        <v>-180871.0345204206</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1206,13 +1206,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>517751.4338739319</v>
+        <v>517716.9792117341</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>472651.0486923354</v>
+        <v>472616.5940301376</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>73642.44708379809</v>
+        <v>73676.90174599591</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>451534.6230678736</v>
+        <v>451504.5749175634</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>451534.6230678736</v>
+        <v>451504.5749175634</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>130879.8131372471</v>
+        <v>130909.8612875574</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>263802.2665402248</v>
+        <v>263784.7113633851</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>263802.2665402248</v>
+        <v>263784.7113633851</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-250975.6168513072</v>
+        <v>-250958.0616744675</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>263785.7668215087</v>
+        <v>263768.2127426713</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>263785.7668215087</v>
+        <v>263768.2127426713</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-202472.7797845087</v>
+        <v>-202455.2257056712</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>266722.3963774357</v>
+        <v>266704.6468755192</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>243488.6938202549</v>
+        <v>243470.9443183384</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>37937.29708157951</v>
+        <v>37955.04658349595</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>198060.9047933366</v>
+        <v>198047.7244888066</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>180808.179815331</v>
+        <v>180794.9995108011</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>28171.22029287117</v>
+        <v>28184.40059740107</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>115569.539031945</v>
+        <v>115561.8482576328</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>115569.539031945</v>
+        <v>115561.8482576328</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-11760.91824494497</v>
+        <v>-11753.22747063284</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>88012.01357885409</v>
+        <v>88006.15666760514</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>88012.01357885409</v>
+        <v>88006.15666760514</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>13934.96786235993</v>
+        <v>13940.82477360887</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>34616.22938451851</v>
+        <v>34613.92578782718</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>34616.22938451851</v>
+        <v>34613.92578782718</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>23847.92927006701</v>
+        <v>23850.23286675835</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>26380.87196231475</v>
+        <v>26379.11640168763</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>26380.87196231475</v>
+        <v>26379.11640168763</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-6958.774598314753</v>
+        <v>-6957.01903768763</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1899,13 +1899,13 @@
         <v>-11026.718022</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-5.6402e-09</v>
+        <v>-6.4324e-09</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-5.6402e-09</v>
+        <v>-6.4324e-09</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>13323.41401375031</v>
+        <v>13322.5273841842</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>13323.41401375031</v>
+        <v>13322.5273841842</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-13323.41401375595</v>
+        <v>-13322.52738419063</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1964,31 +1964,31 @@
         <v>20906.564239</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2.1207e-09</v>
+        <v>-1.5563e-09</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>2.1207e-09</v>
+        <v>-1.5563e-09</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>5011688.25004375</v>
+        <v>5011688.250043751</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13220.95059076399</v>
+        <v>13220.0707798031</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>13220.95059076399</v>
+        <v>13220.0707798031</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-13220.95059076186</v>
+        <v>-13220.07077980465</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2029,13 +2029,13 @@
         <v>-2334.172736</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1.013e-10</v>
+        <v>9.32e-11</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.013e-10</v>
+        <v>9.32e-11</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>13149.67075707729</v>
+        <v>13148.79568955588</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>13149.67075707729</v>
+        <v>13148.79568955588</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-13149.67075707719</v>
+        <v>-13148.79568955578</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2094,13 +2094,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-2.4963e-09</v>
+        <v>-1.3866e-09</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-2.4963e-09</v>
+        <v>-1.3866e-09</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>12968.50860003831</v>
+        <v>12967.64558826511</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>12968.50860003831</v>
+        <v>12967.64558826511</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-12968.50860004081</v>
+        <v>-12967.6455882665</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>2574.024470289222</v>
+        <v>2573.853177391105</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>2574.024470289222</v>
+        <v>2573.853177391105</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-313.1527524846144</v>
+        <v>-312.9814595864969</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>2567.892153520429</v>
+        <v>2567.721268707909</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>2344.207741172148</v>
+        <v>2344.036856359627</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>365.2444969926905</v>
+        <v>365.4153818052115</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2358,31 +2358,31 @@
         <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-9e-11</v>
+        <v>3.705e-09</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-9e-11</v>
+        <v>3.705e-09</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>69404.94659889408</v>
+        <v>69404.94659889178</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>183.0918692379921</v>
+        <v>183.0796850737461</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>183.0918692379921</v>
+        <v>183.0796850737461</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-183.0918692380821</v>
+        <v>-183.0796850700411</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2395,12 +2395,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+          <t>Spark.fi USDT Reserve Uniswap V4 (USDT/USDS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2410,109 +2410,113 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1868.74164</v>
+        <v>219994.2553850041</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>1868.74164</v>
+        <v>219994.2553850041</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-2.18382e-08</v>
+        <v>-2.62944411170806</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-2.18382e-08</v>
+        <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0</v>
+        <v>-2.62944411170806</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>538.7469580157663</v>
+        <v>78570.31601039848</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1.421227051141632</v>
+        <v>0</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.421227051141632</v>
+        <v>-2.62944411170806</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-1.421227072979832</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>0</v>
+        <v>78570.31601039848</v>
       </c>
       <c r="R26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>61.15121926789406</v>
+        <v>0</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>494.7150552250027</v>
+        <v>1868.74164</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>433.5638359571087</v>
+        <v>1868.74164</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1.217080133914307</v>
+        <v>-2.14057e-08</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>1.217080133914307</v>
+        <v>-2.14057e-08</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>499.1597379746905</v>
+        <v>538.74695801446</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>1.316795040594249</v>
+        <v>1.4211324731327</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.316795040594249</v>
+        <v>1.4211324731327</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-0.09971490667994179</v>
+        <v>-1.4211324945384</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2525,17 +2529,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2544,40 +2548,40 @@
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>332.9212943539781</v>
+        <v>61.15121926789406</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>344.9608587271188</v>
+        <v>494.7150552250027</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>12.0395643731406</v>
+        <v>433.5638359571087</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>1.26224901053333</v>
+        <v>1.217080131948199</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>1.26224901053333</v>
+        <v>1.217080131948199</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>336.3854314348162</v>
+        <v>499.159737975814</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.8873926203238416</v>
+        <v>1.316707412199995</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.8873926203238416</v>
+        <v>1.316707412199995</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3748563902094886</v>
+        <v>-0.09962728025179615</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2590,17 +2594,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2609,40 +2613,40 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>332.9212943539781</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>344.9608587271188</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0</v>
+        <v>12.0395643731406</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0</v>
+        <v>1.26224901053333</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0</v>
+        <v>1.26224901053333</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>336.3854314348162</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.7489275694519881</v>
+        <v>0.8873335672513251</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.7489275694519881</v>
+        <v>0.8873335672513251</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.7489275694519881</v>
+        <v>0.3749154432820052</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2655,17 +2659,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2674,40 +2678,40 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>98.60727406618892</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>98.88131626312872</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.2740421969397932</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.2740421969397932</v>
+        <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.2740421969397932</v>
+        <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>98.60727406618892</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.260128290762624</v>
+        <v>0.7488777307751099</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.260128290762624</v>
+        <v>0.7488777307751099</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.01391390617716923</v>
+        <v>-0.7488777307751099</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2720,12 +2724,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2739,40 +2743,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>21.90604334087989</v>
+        <v>98.60727406618892</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>21.90659475982325</v>
+        <v>98.88131626312872</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.0005514189433507683</v>
+        <v>0.2740421969397932</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>1.025604740466448e-05</v>
+        <v>0.2740421969397932</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>1.025604740466448e-05</v>
+        <v>0.2740421969397932</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>21.90648786754442</v>
+        <v>98.60727406618892</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.05778982635471135</v>
+        <v>0.2601109800768394</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.05778982635471135</v>
+        <v>0.2601109800768394</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.05777957030730669</v>
+        <v>0.01393121686295385</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2785,12 +2789,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2800,44 +2804,44 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>1.210584</v>
+        <v>21.90604334087989</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1.210594</v>
+        <v>21.90659475982325</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>1e-05</v>
+        <v>0.0005514189433507683</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>1e-05</v>
+        <v>1.025604740466448e-05</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>1e-05</v>
+        <v>1.025604740466448e-05</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>1.210584</v>
+        <v>21.90648786754442</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.003193548850495581</v>
+        <v>0.05778598063103924</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.003193548850495581</v>
+        <v>0.05778598063103924</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.003183548850495582</v>
+        <v>-0.05777572458363457</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2850,12 +2854,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2865,109 +2869,113 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.057354</v>
+        <v>0</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.057463</v>
+        <v>220000.0301712902</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.000109</v>
+        <v>220000.0301712902</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.000109</v>
+        <v>0.0310806706219395</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.000109</v>
+        <v>0</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0</v>
+        <v>0.0310806706219395</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.057354</v>
+        <v>78571.42824664984</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.0001513011908065228</v>
+        <v>0</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.0001513011908065228</v>
+        <v>0.0310806706219395</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-4.230119080652278e-05</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>0</v>
+        <v>78571.42824664984</v>
       </c>
       <c r="R33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.00631</v>
+        <v>1.210584</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.006319</v>
+        <v>1.210594</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>9e-06</v>
+        <v>1e-05</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>9e-06</v>
+        <v>1e-05</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>9e-06</v>
+        <v>1e-05</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.00631</v>
+        <v>1.210584</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>1.664592729346094e-05</v>
+        <v>0.003193336330279012</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>1.664592729346094e-05</v>
+        <v>0.003193336330279012</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-7.645927293460939e-06</v>
+        <v>-0.003183336330279012</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2980,12 +2988,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2999,40 +3007,40 @@
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0.005739369858543872</v>
+        <v>0.057354</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.005740696354252308</v>
+        <v>0.057463</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1.326495708436e-06</v>
+        <v>0.000109</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1.326495708436e-06</v>
+        <v>0.000109</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>1.326495708436e-06</v>
+        <v>0.000109</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.005739369858543872</v>
+        <v>0.057354</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>1.514059166015887e-05</v>
+        <v>0.0001512911222078125</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>1.514059166015887e-05</v>
+        <v>0.0001512911222078125</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-1.381409595172287e-05</v>
+        <v>-4.229112220781246e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3045,17 +3053,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3064,40 +3072,40 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.001688</v>
+        <v>0.00631</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.001692</v>
+        <v>0.006319</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>4e-06</v>
+        <v>9e-06</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>4e-06</v>
+        <v>9e-06</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>4e-06</v>
+        <v>9e-06</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.001688</v>
+        <v>0.00631</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>4.452983402751516e-06</v>
+        <v>1.664481956151788e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>4.452983402751516e-06</v>
+        <v>1.664481956151788e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-4.52983402751516e-07</v>
+        <v>-7.644819561517882e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3110,12 +3118,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3125,44 +3133,44 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005739369858543872</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005740696354252308</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0</v>
+        <v>1.326495708436e-06</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0</v>
+        <v>1.326495708436e-06</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0</v>
+        <v>1.326495708436e-06</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005739369858543872</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>3.271530589331472e-06</v>
+        <v>1.513958410337197e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>3.271530589331472e-06</v>
+        <v>1.513958410337197e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-3.271530589331472e-06</v>
+        <v>-1.381308839493597e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3175,17 +3183,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3194,40 +3202,40 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.000518423030497757</v>
+        <v>0.001688</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.000519245328957253</v>
+        <v>0.001692</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>8.22298459496e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>8.22298459495e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>8.22298459495e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.000518423030497757</v>
+        <v>0.001688</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.367612055930483e-06</v>
+        <v>4.452687071290362e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.367612055930483e-06</v>
+        <v>4.452687071290362e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-5.453135964354829e-07</v>
+        <v>-4.526870712903622e-07</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3240,12 +3248,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3255,14 +3263,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>0</v>
@@ -3280,19 +3288,19 @@
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.975781241118573e-07</v>
+        <v>3.271312879685587e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.975781241118573e-07</v>
+        <v>3.271312879685587e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-1.975781241118573e-07</v>
+        <v>-3.271312879685587e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3305,12 +3313,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3324,40 +3332,40 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0</v>
+        <v>0.000518423030497757</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0</v>
+        <v>0.000519245328957253</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0</v>
+        <v>8.22298459496e-07</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0</v>
+        <v>8.22298459495e-07</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>0</v>
+        <v>8.22298459495e-07</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0</v>
+        <v>0.000518423030497757</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0</v>
+        <v>1.367521045827329e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0</v>
+        <v>1.367521045827329e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0</v>
+        <v>-5.452225863323293e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3370,12 +3378,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3385,14 +3393,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>0</v>
@@ -3410,19 +3418,19 @@
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0</v>
+        <v>1.975649759348006e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0</v>
+        <v>1.975649759348006e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0</v>
+        <v>-1.975649759348006e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3435,12 +3443,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3450,7 +3458,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
@@ -3463,31 +3471,31 @@
         <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0</v>
+        <v>3.912e-09</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0</v>
+        <v>3.912e-09</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0</v>
+        <v>1.400207142857143e-08</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0</v>
+        <v>3.693533318796456e-11</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0</v>
+        <v>3.693533318796456e-11</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0</v>
+        <v>3.875064666812036e-09</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3500,12 +3508,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3515,7 +3523,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
@@ -3565,12 +3573,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3580,7 +3588,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
@@ -3608,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
         <v>0</v>
@@ -3625,21 +3633,17 @@
       <c r="R44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3699,12 +3703,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3714,7 +3718,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
@@ -3727,13 +3731,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>891779.9999999979</v>
+        <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>891779.9999999979</v>
+        <v>0</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -3751,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>891779.9999999979</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3764,12 +3768,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3779,7 +3783,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3792,13 +3796,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>4.3675e-08</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>4.3675e-08</v>
+        <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
@@ -3807,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" s="6" t="n">
         <v>0</v>
@@ -3816,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>4.3675e-08</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3824,17 +3828,21 @@
       <c r="R47" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3844,7 +3852,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -3857,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-4.7472e-08</v>
+        <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-4.7472e-08</v>
+        <v>0</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>21.29666254724045</v>
+        <v>0</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>0</v>
@@ -3881,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>-4.7472e-08</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3889,26 +3897,22 @@
       <c r="R48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3917,31 +3921,31 @@
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>0</v>
+        <v>891779.999999939</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0</v>
+        <v>891779.999999939</v>
       </c>
       <c r="K49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3950,39 +3954,35 @@
         <v>0</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0</v>
+        <v>891779.999999939</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3995,22 +3995,22 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0</v>
+        <v>4.37305e-08</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0</v>
+        <v>4.37305e-08</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0</v>
+        <v>21.29666244674675</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>0</v>
@@ -4019,30 +4019,34 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0</v>
+        <v>4.37305e-08</v>
       </c>
       <c r="Q50" s="6" t="n">
-        <v>0</v>
+        <v>21.29666244674675</v>
       </c>
       <c r="R50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4051,10 +4055,10 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
@@ -4072,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="M51" s="7" t="n">
         <v>0</v>
@@ -4087,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
@@ -4101,29 +4105,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
@@ -4141,10 +4145,10 @@
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" s="6" t="n">
         <v>0</v>
@@ -4156,31 +4160,27 @@
         <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4210,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4239,168 +4239,250 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>S48</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>USDS raw (Optimism — POL)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>optimism</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>USDS raw (Unichain — POL)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unichain</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Pricing cat.</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Position SoM</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Position EoM</t>
         </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>S56</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>207131500.431691</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>287780830.420175</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="n">
-        <v>120038508.359851</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>387977397.421864</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4414,51 +4496,107 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>285387.136685</v>
+        <v>207131500.431691</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>94443.720094</v>
+        <v>287780830.420175</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDT vault</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>120038508.359851</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>387977397.421864</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>285387.136685</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>94443.720094</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>S60</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>avalanche_c</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E63" s="6" t="n">
         <v>95656876.179346</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F63" s="6" t="n">
         <v>152857139.195815</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" s="9" t="n">
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4513,7 +4651,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>2508076304.951767</v>
+        <v>2507919163.266385</v>
       </c>
     </row>
     <row r="6">
@@ -4533,7 +4671,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1508076304.951767</v>
+        <v>1507919163.266385</v>
       </c>
     </row>
     <row r="8">
@@ -4573,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.04055229619917895</v>
+        <v>0.04055213531137732</v>
       </c>
     </row>
     <row r="12">
@@ -4583,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-25.6770569728142</v>
+        <v>-25.67866585083047</v>
       </c>
     </row>
     <row r="13">
@@ -4603,7 +4741,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>8122887.021486939</v>
+        <v>8122378.087945241</v>
       </c>
     </row>
     <row r="16">
@@ -4613,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>7647762.426092711</v>
+        <v>7647253.492551014</v>
       </c>
     </row>
     <row r="17">
@@ -4663,10 +4801,10 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1508076304.951767</v>
+        <v>1507919163.266385</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4884194.879047058</v>
+        <v>4883685.945505361</v>
       </c>
     </row>
     <row r="23">
@@ -4688,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>7486766.172836288</v>
+        <v>7486257.239294591</v>
       </c>
     </row>
     <row r="25">
@@ -4698,7 +4836,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>3733.877754048192</v>
+        <v>3731.279390607106</v>
       </c>
     </row>
     <row r="26">
@@ -4708,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>7490500.050590336</v>
+        <v>7489988.518685198</v>
       </c>
     </row>
     <row r="28">
@@ -4735,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>7486766.172836288</v>
+        <v>7486257.239294591</v>
       </c>
     </row>
     <row r="32">
@@ -4745,7 +4883,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2566219.823131723</v>
+        <v>-2566728.75667342</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -4875,7 +5013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5035,6 +5173,86 @@
       </c>
       <c r="J5" s="6" t="n">
         <v>3733.877754048192</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S61</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PYUSD in PYUSD/USDS Uniswap V4</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.0310806706219395</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.0310806706219395</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S62</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>USDT in USDT/USDS Uniswap V4</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-2.62944411170806</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-2.62944411170806</v>
       </c>
     </row>
   </sheetData>
@@ -6056,16 +6274,16 @@
         <v>105839845.8064453</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>88579423.51548044</v>
+        <v>88869303.80928044</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>64115392.71372245</v>
+        <v>64265513.97577874</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>171708475.8308767</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2512556553.218271</v>
+        <v>2512116551.662415</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -6083,7 +6301,7 @@
         <v>0.03668000007901918</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>273652.5918196291</v>
+        <v>273601.6979060001</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>362162.940994632</v>
@@ -6105,16 +6323,16 @@
         <v>106244104.3858212</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>86620267.0626184</v>
+        <v>86895251.75446941</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>65580982.41636725</v>
+        <v>65745995.83678398</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>172162721.2920108</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2536169076.683437</v>
+        <v>2535729078.571169</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -6132,7 +6350,7 @@
         <v>0.03668000007901918</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>276383.7951842653</v>
+        <v>276332.9016689478</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>364936.3557712165</v>
@@ -6154,16 +6372,16 @@
         <v>106190262.4644004</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>87350484.05449657</v>
+        <v>87637531.43673757</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>54036624.62865652</v>
+        <v>54189574.80195495</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>172114598.1401009</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>2549499917.625371</v>
+        <v>2549059920.069831</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -6181,7 +6399,7 @@
         <v>0.03668000007901918</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>277925.7412489351</v>
+        <v>277874.847798013</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>365215.6623250113</v>
@@ -6203,16 +6421,16 @@
         <v>105749238.4054566</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>87831880.21825115</v>
+        <v>88124070.48399515</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>52509971.5607803</v>
+        <v>52657779.77695882</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>172130873.8331746</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>2544991385.337146</v>
+        <v>2544551386.855224</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -6230,7 +6448,7 @@
         <v>0.03668000007901918</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>277404.2502455133</v>
+        <v>277353.3566874388</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>364524.1393745443</v>
@@ -6252,16 +6470,16 @@
         <v>105650029.128424</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>85638134.64147896</v>
+        <v>85902523.83990195</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>67269600.88137993</v>
+        <v>67445208.4085051</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>170384756.6215345</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>2522080595.466539</v>
+        <v>2521640598.740991</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -6279,7 +6497,7 @@
         <v>0.03668000007901918</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>274754.2147051196</v>
+        <v>274703.3213502006</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>363114.1247107522</v>
@@ -6301,16 +6519,16 @@
         <v>105656287.4630376</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>72235071.09160909</v>
+        <v>72486558.1043621</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>66054992.5679894</v>
+        <v>66243500.21978736</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>164698591.325855</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>2504438391.182117</v>
+        <v>2503998396.517566</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -6328,7 +6546,7 @@
         <v>0.03668000007901918</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>272713.5836911454</v>
+        <v>272662.690574617</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>358725.7219450316</v>
@@ -6350,16 +6568,16 @@
         <v>105835028.346491</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>53793836.9446341</v>
+        <v>54018304.47331911</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>67036073.21227839</v>
+        <v>67251602.87866101</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>164389729.7446583</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>2505790415.935942</v>
+        <v>2505350418.740875</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -6377,7 +6595,7 @@
         <v>0.03668000007901918</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>272869.9691178096</v>
+        <v>272819.0757085824</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>356847.4829846853</v>
@@ -6399,16 +6617,16 @@
         <v>105770621.9190764</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>59097324.34855221</v>
+        <v>59349402.28568321</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>58569838.14097168</v>
+        <v>58757754.71710162</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>164299122.520608</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>2503884834.831986</v>
+        <v>2503444840.318725</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -6426,7 +6644,7 @@
         <v>0.03668000007901918</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>272649.5551696609</v>
+        <v>272598.6620706317</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>356243.3116253272</v>
@@ -6448,16 +6666,16 @@
         <v>105484587.1280991</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>78466307.67748198</v>
+        <v>78739566.82541898</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>51725728.12275265</v>
+        <v>51892463.07594856</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>161025661.214919</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>2472464753.659592</v>
+        <v>2472024759.558458</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -6475,7 +6693,7 @@
         <v>0.03668000007901918</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>269015.2705265231</v>
+        <v>268964.3774751638</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>353646.0304370871</v>
@@ -6497,16 +6715,16 @@
         <v>105774524.3487542</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>57961427.91663297</v>
+        <v>58227869.12398098</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>44100083.55514738</v>
+        <v>44273636.63335567</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>161097957.4296974</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>2581256156.67179</v>
+        <v>2580816162.386234</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>0.04000000189078801</v>
@@ -6524,7 +6742,7 @@
         <v>0.03668000007901918</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>281598.908458688</v>
+        <v>281548.015385997</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>363017.777457673</v>
@@ -6549,7 +6767,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" s="12" t="n">
-        <v>7647762.426092711</v>
+        <v>7647253.492551014</v>
       </c>
       <c r="O35" s="12" t="n">
         <v>10052985.99596801</v>

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-07T00:03:19+00:00</t>
+          <t>2026-07-07T14:38:36+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10291414.08057339</v>
+        <v>10291414.08057337</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11428640.93676807</v>
+        <v>11428640.93676805</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>10291414.08057339</v>
+        <v>10291414.08057337</v>
       </c>
     </row>
     <row r="23">
@@ -641,7 +641,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1690208.869058825</v>
+        <v>1690208.869058804</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-07T14:38:36+00:00</t>
+          <t>2026-07-10T11:08:58+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1565111.570394413</v>
+        <v>1565143.19497787</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1565111.570394413</v>
+        <v>1565143.19497787</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-426583.6394769294</v>
+        <v>-426615.2640603865</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1384746.022424032</v>
+        <v>1384774.002548249</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1384746.022424032</v>
+        <v>1384774.002548249</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1440253.977575968</v>
+        <v>1440225.997451751</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1203648.465537357</v>
+        <v>1203672.78641139</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1203648.465537357</v>
+        <v>1203672.78641139</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>49450.1082699095</v>
+        <v>49425.78739587632</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>90251565.90411383</v>
@@ -1072,13 +1072,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>616355.3170515335</v>
+        <v>616367.7711030734</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>616355.3170515335</v>
+        <v>616367.7711030734</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>102060.1633355013</v>
+        <v>102047.7092839615</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>69623450.80112581</v>
@@ -1141,13 +1141,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>593315.8315224206</v>
+        <v>593327.8200390129</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>593315.8315224206</v>
+        <v>593327.8200390129</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-180871.0345204206</v>
+        <v>-180883.0230370129</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1206,13 +1206,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>517716.9792117341</v>
+        <v>517727.4401808599</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>472616.5940301376</v>
+        <v>472627.0549992634</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>73676.90174599591</v>
+        <v>73666.44077687016</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>451504.5749175634</v>
+        <v>451513.6980014258</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>451504.5749175634</v>
+        <v>451513.6980014258</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>130909.8612875574</v>
+        <v>130900.7382036949</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>263784.7113633851</v>
+        <v>263790.0413869931</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>263784.7113633851</v>
+        <v>263790.0413869931</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-250958.0616744675</v>
+        <v>-250963.3916980755</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>263768.2127426713</v>
+        <v>263773.5424329087</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>263768.2127426713</v>
+        <v>263773.5424329087</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-202455.2257056712</v>
+        <v>-202460.5553959087</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>266704.6468755192</v>
+        <v>266710.0358992305</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>243470.9443183384</v>
+        <v>243476.3333420496</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>37955.04658349595</v>
+        <v>37949.65755978475</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>198047.7244888066</v>
+        <v>198051.7262334171</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>180794.9995108011</v>
+        <v>180799.0012554115</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>28184.40059740107</v>
+        <v>28180.39885279062</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>115561.8482576328</v>
+        <v>115564.1832958396</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>115561.8482576328</v>
+        <v>115564.1832958396</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-11753.22747063284</v>
+        <v>-11755.56250883958</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>88006.15666760514</v>
+        <v>88007.93491658045</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>88006.15666760514</v>
+        <v>88007.93491658045</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>13940.82477360887</v>
+        <v>13939.04652463358</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>34613.92578782718</v>
+        <v>34614.62519546403</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>34613.92578782718</v>
+        <v>34614.62519546403</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>23850.23286675835</v>
+        <v>23849.5334591215</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>26379.11640168763</v>
+        <v>26379.64941708663</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>26379.11640168763</v>
+        <v>26379.64941708663</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-6957.01903768763</v>
+        <v>-6957.552053086628</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1871,17 +1871,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1890,40 +1890,40 @@
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>4994817.315553</v>
+        <v>5000000</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>4983790.597531</v>
+        <v>5000000</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-11026.718022</v>
+        <v>0</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-6.4324e-09</v>
+        <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-6.4324e-09</v>
+        <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>5050529.234246395</v>
+        <v>5000000</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>13322.5273841842</v>
+        <v>13189.5054564928</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>13322.5273841842</v>
+        <v>13189.5054564928</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-13322.52738419063</v>
+        <v>-13189.5054564928</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1936,17 +1936,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1955,40 +1955,40 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>4979093.435761</v>
+        <v>5000000</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>5000000</v>
+        <v>4997665.827264</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>20906.564239</v>
+        <v>-2334.172736</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-1.5563e-09</v>
+        <v>0</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-1.5563e-09</v>
+        <v>0</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>5011688.250043751</v>
+        <v>4999916.636688</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13220.0707798031</v>
+        <v>13189.2855523211</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>13220.0707798031</v>
+        <v>13189.2855523211</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-13220.07077980465</v>
+        <v>-13189.2855523211</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2001,17 +2001,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2020,40 +2020,40 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>5000000</v>
+        <v>4994817.315553</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>4997665.827264</v>
+        <v>4983790.597531</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-2334.172736</v>
+        <v>-11026.718022</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>9.32e-11</v>
+        <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>9.32e-11</v>
+        <v>0</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>4984668.082129179</v>
+        <v>4994423.504195072</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>13148.79568955588</v>
+        <v>13174.79521212336</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>13148.79568955588</v>
+        <v>13174.79521212336</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-13148.79568955578</v>
+        <v>-13174.79521212336</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2066,17 +2066,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2085,40 +2085,40 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>5000000</v>
+        <v>4979093.435761</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>5000000</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0</v>
+        <v>20906.564239</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-1.3866e-09</v>
+        <v>0</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-1.3866e-09</v>
+        <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4915994.634819037</v>
+        <v>4979840.098769535</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>12967.64558826511</v>
+        <v>13136.32563103648</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>12967.64558826511</v>
+        <v>13136.32563103648</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-12967.6455882665</v>
+        <v>-13136.32563103648</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>2573.853177391105</v>
+        <v>2573.905184568199</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>2573.853177391105</v>
+        <v>2573.905184568199</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-312.9814595864969</v>
+        <v>-313.0334667635918</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>2567.721268707909</v>
+        <v>2567.773151983895</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>2344.036856359627</v>
+        <v>2344.088739635614</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>365.4153818052115</v>
+        <v>365.3634985292247</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2330,146 +2330,146 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Spark.fi USDT Reserve Uniswap V4 (USDT/USDS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0</v>
+        <v>219994.2553850041</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0</v>
+        <v>219994.2553850041</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>3.705e-09</v>
+        <v>-2.62944411170806</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>3.705e-09</v>
+        <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0</v>
+        <v>-2.62944411170806</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>69404.94659889178</v>
+        <v>78570.31601039848</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>183.0796850737461</v>
+        <v>0</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>183.0796850737461</v>
+        <v>-2.62944411170806</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-183.0796850700411</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>0</v>
+        <v>78570.31601039848</v>
       </c>
       <c r="R25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Uniswap V4 (USDT/USDS)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>0</v>
+        <v>61.15121926789406</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>219994.2553850041</v>
+        <v>494.7150552250027</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>219994.2553850041</v>
+        <v>433.5638359571087</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-2.62944411170806</v>
+        <v>1.217080131948199</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0</v>
+        <v>1.217080131948199</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-2.62944411170806</v>
+        <v>0</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>78570.31601039848</v>
+        <v>499.159737975814</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0</v>
+        <v>1.316734017538703</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>-2.62944411170806</v>
+        <v>1.316734017538703</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0</v>
+        <v>-0.09965388559050389</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>78570.31601039848</v>
+        <v>0</v>
       </c>
       <c r="R26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2479,44 +2479,44 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0</v>
+        <v>332.9212943539781</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1868.74164</v>
+        <v>344.9608587271188</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>1868.74164</v>
+        <v>12.0395643731406</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-2.14057e-08</v>
+        <v>1.26224901053333</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-2.14057e-08</v>
+        <v>1.26224901053333</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>538.74695801446</v>
+        <v>336.3854314348162</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>1.4211324731327</v>
+        <v>0.8873514966788385</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.4211324731327</v>
+        <v>0.8873514966788385</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-1.4211324945384</v>
+        <v>0.3748975138544917</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2529,12 +2529,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2548,40 +2548,40 @@
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>61.15121926789406</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>494.7150552250027</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>433.5638359571087</v>
+        <v>0</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>1.217080131948199</v>
+        <v>0</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>1.217080131948199</v>
+        <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>499.159737975814</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>1.316707412199995</v>
+        <v>0.7488928625693819</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.316707412199995</v>
+        <v>0.7488928625693819</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-0.09962728025179615</v>
+        <v>-0.7488928625693819</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2594,12 +2594,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2613,40 +2613,40 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>332.9212943539781</v>
+        <v>98.60727406618892</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>344.9608587271188</v>
+        <v>98.88131626312872</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>12.0395643731406</v>
+        <v>0.2740421969397932</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>1.26224901053333</v>
+        <v>0.2740421969397932</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>1.26224901053333</v>
+        <v>0.2740421969397932</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>336.3854314348162</v>
+        <v>98.60727406618892</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.8873335672513251</v>
+        <v>0.2601162358691759</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.8873335672513251</v>
+        <v>0.2601162358691759</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.3749154432820052</v>
+        <v>0.01392596107061728</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2659,32 +2659,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>0</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>1868.74164</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0</v>
+        <v>1868.74164</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>0</v>
@@ -2699,19 +2699,19 @@
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>66.74077285714286</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.7488777307751099</v>
+        <v>0.1760555575539664</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.7488777307751099</v>
+        <v>0.1760555575539664</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-0.7488777307751099</v>
+        <v>-0.1760555575539664</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2724,12 +2724,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2743,40 +2743,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>98.60727406618892</v>
+        <v>21.90604334087989</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>98.88131626312872</v>
+        <v>21.90659475982325</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.2740421969397932</v>
+        <v>0.0005514189433507683</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.2740421969397932</v>
+        <v>1.025604740466448e-05</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.2740421969397932</v>
+        <v>1.025604740466448e-05</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>98.60727406618892</v>
+        <v>21.90648786754442</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2601109800768394</v>
+        <v>0.05778714825231409</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2601109800768394</v>
+        <v>0.05778714825231409</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.01393121686295385</v>
+        <v>-0.05777689220490943</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2789,12 +2789,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2804,62 +2804,66 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>21.90604334087989</v>
+        <v>0</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>21.90659475982325</v>
+        <v>220000.0301712902</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.0005514189433507683</v>
+        <v>220000.0301712902</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>1.025604740466448e-05</v>
+        <v>0.0310806706219395</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>1.025604740466448e-05</v>
+        <v>0</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0</v>
+        <v>0.0310806706219395</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>21.90648786754442</v>
+        <v>78571.42824664984</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.05778598063103924</v>
+        <v>0</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.05778598063103924</v>
+        <v>0.0310806706219395</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.05777572458363457</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>0</v>
+        <v>78571.42824664984</v>
       </c>
       <c r="R32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2869,66 +2873,62 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0</v>
+        <v>1.210584</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>220000.0301712902</v>
+        <v>1.210594</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>220000.0301712902</v>
+        <v>1e-05</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.0310806706219395</v>
+        <v>1e-05</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.0310806706219395</v>
+        <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>78571.42824664984</v>
+        <v>1.210584</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0</v>
+        <v>0.003193400854708576</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.0310806706219395</v>
+        <v>0.003193400854708576</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0</v>
+        <v>-0.003183400854708575</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>78571.42824664984</v>
+        <v>0</v>
       </c>
       <c r="R33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2938,44 +2938,44 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>1.210584</v>
+        <v>0.057354</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1.210594</v>
+        <v>0.057463</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>1e-05</v>
+        <v>0.000109</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>1e-05</v>
+        <v>0.000109</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1e-05</v>
+        <v>0.000109</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>1.210584</v>
+        <v>0.057354</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.003193336330279012</v>
+        <v>0.0001512941791903376</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.003193336330279012</v>
+        <v>0.0001512941791903376</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.003183336330279012</v>
+        <v>-4.22941791903376e-05</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2988,17 +2988,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3007,40 +3007,40 @@
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0.057354</v>
+        <v>0.00631</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.057463</v>
+        <v>0.006319</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.000109</v>
+        <v>9e-06</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.000109</v>
+        <v>9e-06</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.000109</v>
+        <v>9e-06</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.057354</v>
+        <v>0.00631</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001512911222078125</v>
+        <v>1.664515588609391e-05</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001512911222078125</v>
+        <v>1.664515588609391e-05</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-4.229112220781246e-05</v>
+        <v>-7.645155886093912e-06</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3053,17 +3053,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3072,40 +3072,40 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.00631</v>
+        <v>0.005739369858543872</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.006319</v>
+        <v>0.005740696354252308</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>9e-06</v>
+        <v>1.326495708436e-06</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>9e-06</v>
+        <v>1.326495708436e-06</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>9e-06</v>
+        <v>1.326495708436e-06</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.00631</v>
+        <v>0.005739369858543872</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.664481956151788e-05</v>
+        <v>1.513989001321894e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.664481956151788e-05</v>
+        <v>1.513989001321894e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-7.644819561517882e-06</v>
+        <v>-1.381339430478294e-05</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3118,17 +3118,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3137,40 +3137,40 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.005739369858543872</v>
+        <v>0.001688</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.005740696354252308</v>
+        <v>0.001692</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>1.326495708436e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1.326495708436e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>1.326495708436e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.005739369858543872</v>
+        <v>0.001688</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.513958410337197e-05</v>
+        <v>4.452777042111969e-06</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.513958410337197e-05</v>
+        <v>4.452777042111969e-06</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.381308839493597e-05</v>
+        <v>-4.527770421119688e-07</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3183,59 +3183,59 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.001688</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.001692</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.001688</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>4.452687071290362e-06</v>
+        <v>3.271378979706272e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>4.452687071290362e-06</v>
+        <v>3.271378979706272e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-4.526870712903622e-07</v>
+        <v>-3.271378979706272e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3248,12 +3248,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3263,44 +3263,44 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.000518423030497757</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.000519245328957253</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0</v>
+        <v>8.22298459496e-07</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0</v>
+        <v>8.22298459495e-07</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0</v>
+        <v>8.22298459495e-07</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.000518423030497757</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>3.271312879685587e-06</v>
+        <v>1.36754867790434e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>3.271312879685587e-06</v>
+        <v>1.36754867790434e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-3.271312879685587e-06</v>
+        <v>-5.452502184093398e-07</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3313,12 +3313,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3328,44 +3328,44 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.000518423030497757</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.000519245328957253</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>8.22298459496e-07</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>8.22298459495e-07</v>
+        <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>8.22298459495e-07</v>
+        <v>0</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.000518423030497757</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.367521045827329e-06</v>
+        <v>1.975689679250125e-07</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.367521045827329e-06</v>
+        <v>1.975689679250125e-07</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-5.452225863323293e-07</v>
+        <v>-1.975689679250125e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3378,12 +3378,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3393,14 +3393,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>0</v>
@@ -3418,19 +3418,19 @@
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.975649759348006e-07</v>
+        <v>0</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.975649759348006e-07</v>
+        <v>0</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.975649759348006e-07</v>
+        <v>0</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3443,12 +3443,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
@@ -3471,31 +3471,31 @@
         <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>3.912e-09</v>
+        <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>3.912e-09</v>
+        <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>1.400207142857143e-08</v>
+        <v>0</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>3.693533318796456e-11</v>
+        <v>0</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>3.693533318796456e-11</v>
+        <v>0</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>3.875064666812036e-09</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3508,12 +3508,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
@@ -3573,12 +3573,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
@@ -3638,12 +3638,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" s="6" t="n">
         <v>0</v>
@@ -3698,17 +3698,21 @@
       <c r="R45" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3768,12 +3772,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3783,7 +3787,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3796,13 +3800,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0</v>
+        <v>891779.999999939</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0</v>
+        <v>891779.999999939</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
@@ -3811,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" s="6" t="n">
         <v>0</v>
@@ -3820,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0</v>
+        <v>891779.999999939</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3828,21 +3832,17 @@
       <c r="R47" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -3902,12 +3902,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3930,13 +3930,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>891779.999999939</v>
+        <v>0</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>891779.999999939</v>
+        <v>0</v>
       </c>
       <c r="K49" s="6" t="n">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>891779.999999939</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
         <v>0</v>
@@ -3962,22 +3962,26 @@
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3986,28 +3990,28 @@
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>4.37305e-08</v>
+        <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>4.37305e-08</v>
+        <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>21.29666244674675</v>
+        <v>65170000</v>
       </c>
       <c r="M50" s="7" t="n">
         <v>0</v>
@@ -4019,10 +4023,10 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>4.37305e-08</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="6" t="n">
-        <v>21.29666244674675</v>
+        <v>65170000</v>
       </c>
       <c r="R50" s="6" t="n">
         <v>0</v>
@@ -4036,29 +4040,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
@@ -4076,10 +4080,10 @@
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0</v>
@@ -4091,26 +4095,22 @@
         <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
@@ -4145,10 +4145,10 @@
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" s="6" t="n">
         <v>0</v>
@@ -4160,27 +4160,31 @@
         <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S48</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>USDS raw (Optimism — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4189,10 +4193,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>90000000</v>
+        <v>89900000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>90000000</v>
+        <v>89900000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4210,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>90000000</v>
+        <v>89900000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4225,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>90000000</v>
+        <v>89900000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4239,17 +4243,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>USDS raw (Unichain — POL)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4308,17 +4312,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4327,10 +4331,10 @@
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="G55" s="6" t="n">
         <v>0</v>
@@ -4348,10 +4352,10 @@
         <v>0</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" s="6" t="n">
         <v>0</v>
@@ -4363,16 +4367,12 @@
         <v>0</v>
       </c>
       <c r="Q55" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R55" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10291414.08057337</v>
+        <v>10291414.08057537</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11428640.93676805</v>
+        <v>11428640.93677005</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>10291414.08057337</v>
+        <v>10291414.08057537</v>
       </c>
     </row>
     <row r="23">
@@ -641,7 +641,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1690208.869058804</v>
+        <v>1690208.869060804</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-10T11:08:58+00:00</t>
+          <t>2026-07-13T18:20:13+00:00</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
         <v>1203672.78641139</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>49425.78739587632</v>
+        <v>49425.78739587629</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>90251565.90411383</v>
@@ -1078,7 +1078,7 @@
         <v>616367.7711030734</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>102047.7092839615</v>
+        <v>102047.7092839614</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>69623450.80112581</v>
@@ -1123,13 +1123,13 @@
         <v>114111429.588736</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>412444.797002</v>
+        <v>412444.797003</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>412444.797002</v>
+        <v>412444.797003</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>0</v>
@@ -1141,13 +1141,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>593327.8200390129</v>
+        <v>593327.8200390128</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>593327.8200390129</v>
+        <v>593327.8200390128</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-180883.0230370129</v>
+        <v>-180883.0230360128</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1537,7 +1537,7 @@
         <v>180799.0012554115</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>28180.39885279062</v>
+        <v>28180.39885279061</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1667,7 +1667,7 @@
         <v>88007.93491658045</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>13939.04652463358</v>
+        <v>13939.04652463357</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1834,31 +1834,31 @@
         <v>-821.531306</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>19422.097364</v>
+        <v>19422.097365</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>19422.097364</v>
+        <v>19422.097365</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>10000242.05005379</v>
+        <v>10000242.05005375</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>26379.64941708663</v>
+        <v>26379.64941708653</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>26379.64941708663</v>
+        <v>26379.64941708653</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-6957.552053086628</v>
+        <v>-6957.552052086534</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>13136.32563103648</v>
+        <v>13136.32563103649</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>13136.32563103648</v>
+        <v>13136.32563103649</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-13136.32563103648</v>
+        <v>-13136.32563103649</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2252,7 +2252,7 @@
         <v>2573.905184568199</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-313.0334667635918</v>
+        <v>-313.0334667635919</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2451,7 +2451,7 @@
         <v>1.316734017538703</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-0.09965388559050389</v>
+        <v>-0.09965388559050392</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
         <v>0.2601162358691759</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.01392596107061728</v>
+        <v>0.01392596107061727</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2910,7 +2910,7 @@
         <v>0.003193400854708576</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.003183400854708575</v>
+        <v>-0.003183400854708576</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
         <v>4.452777042111969e-06</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-4.527770421119688e-07</v>
+        <v>-4.527770421119689e-07</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3276,13 +3276,13 @@
         <v>8.22298459496e-07</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>8.22298459495e-07</v>
+        <v>8.22298459496e-07</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>8.22298459495e-07</v>
+        <v>8.22298459496e-07</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>1.36754867790434e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-5.452502184093398e-07</v>
+        <v>-5.452502184083397e-07</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>7486257.239294591</v>
+        <v>7518418.384692316</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>7489988.518685198</v>
+        <v>7522149.664082923</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>7486257.239294591</v>
+        <v>7518418.384692316</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>10052985.99596801</v>
+        <v>10085147.14136574</v>
       </c>
     </row>
     <row r="19">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-7486257.239294591</v>
+        <v>-7518418.384692316</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1690208.869060804</v>
+        <v>1658047.72366308</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-13T18:20:13+00:00</t>
+          <t>2026-07-31T00:12:57+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1565143.19497787</v>
+        <v>1571725.53174897</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1565143.19497787</v>
+        <v>1571725.53174897</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-426615.2640603865</v>
+        <v>-433197.6008314866</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1384774.002548249</v>
+        <v>1390597.78203749</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1384774.002548249</v>
+        <v>1390597.78203749</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1440225.997451751</v>
+        <v>1434402.21796251</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1203672.78641139</v>
+        <v>1208734.930033642</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1203672.78641139</v>
+        <v>1208734.930033642</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>49425.78739587629</v>
+        <v>44363.64377362438</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>90251565.90411383</v>
@@ -1072,13 +1072,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>616367.7711030734</v>
+        <v>618959.9558036625</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>616367.7711030734</v>
+        <v>618959.9558036625</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>102047.7092839614</v>
+        <v>99455.52458337236</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>69623450.80112581</v>
@@ -1141,13 +1141,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>593327.8200390128</v>
+        <v>595823.1083549261</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>593327.8200390128</v>
+        <v>595823.1083549261</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-180883.0230360128</v>
+        <v>-183378.3113519261</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1206,13 +1206,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>517727.4401808599</v>
+        <v>519904.7849617367</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>472627.0549992634</v>
+        <v>474804.3997801403</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>73666.44077687016</v>
+        <v>71489.0959959933</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>451513.6980014258</v>
+        <v>453412.5755140691</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>451513.6980014258</v>
+        <v>453412.5755140691</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>130900.7382036949</v>
+        <v>129001.8606910516</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>263790.0413869931</v>
+        <v>264899.4318215828</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>263790.0413869931</v>
+        <v>264899.4318215828</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-250963.3916980755</v>
+        <v>-252072.7821326652</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>263773.5424329087</v>
+        <v>264882.8634798075</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>263773.5424329087</v>
+        <v>264882.8634798075</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-202460.5553959087</v>
+        <v>-203569.8764428075</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>266710.0358992305</v>
+        <v>267831.7066077983</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>243476.3333420496</v>
+        <v>244598.0040506175</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>37949.65755978475</v>
+        <v>36827.98685121693</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>198051.7262334171</v>
+        <v>198884.6488467276</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>180799.0012554115</v>
+        <v>181631.923868722</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>28180.39885279061</v>
+        <v>27347.47623948014</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>115564.1832958396</v>
+        <v>116050.1978506555</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>115564.1832958396</v>
+        <v>116050.1978506555</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-11755.56250883958</v>
+        <v>-12241.57706365552</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>88007.93491658045</v>
+        <v>88378.05943171031</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>88007.93491658045</v>
+        <v>88378.05943171031</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>13939.04652463357</v>
+        <v>13568.92200950371</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>34614.62519546403</v>
+        <v>34760.19981187808</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>34614.62519546403</v>
+        <v>34760.19981187808</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>23849.5334591215</v>
+        <v>23703.95884270745</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>26379.64941708653</v>
+        <v>26490.59117431615</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>26379.64941708653</v>
+        <v>26490.59117431615</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-6957.552052086534</v>
+        <v>-7068.493809316149</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>13189.5054564928</v>
+        <v>13244.97499246719</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>13189.5054564928</v>
+        <v>13244.97499246719</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-13189.5054564928</v>
+        <v>-13244.97499246719</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1982,13 +1982,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13189.2855523211</v>
+        <v>13244.75416347064</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>13189.2855523211</v>
+        <v>13244.75416347064</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-13189.2855523211</v>
+        <v>-13244.75416347064</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>13174.79521212336</v>
+        <v>13230.20288297081</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>13174.79521212336</v>
+        <v>13230.20288297081</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-13174.79521212336</v>
+        <v>-13230.20288297081</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>13136.32563103649</v>
+        <v>13191.57151493757</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>13136.32563103649</v>
+        <v>13191.57151493757</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-13136.32563103649</v>
+        <v>-13191.57151493757</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>2573.905184568199</v>
+        <v>2584.729951781878</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>2573.905184568199</v>
+        <v>2584.729951781878</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-313.0334667635919</v>
+        <v>-323.8582339772704</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>2567.773151983895</v>
+        <v>2578.572130436718</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>2344.088739635614</v>
+        <v>2354.887718088436</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>365.3634985292247</v>
+        <v>354.5645200764025</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2445,13 +2445,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1.316734017538703</v>
+        <v>1.322271649347226</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.316734017538703</v>
+        <v>1.322271649347226</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-0.09965388559050392</v>
+        <v>-0.1051915173990273</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2510,13 +2510,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.8873514966788385</v>
+        <v>0.8910833254368854</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.8873514966788385</v>
+        <v>0.8910833254368854</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3748975138544917</v>
+        <v>0.3711656850964448</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2575,13 +2575,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.7488928625693819</v>
+        <v>0.7520423923010526</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.7488928625693819</v>
+        <v>0.7520423923010526</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-0.7488928625693819</v>
+        <v>-0.7520423923010526</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2640,13 +2640,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2601162358691759</v>
+        <v>0.2612101758164062</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2601162358691759</v>
+        <v>0.2612101758164062</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.01392596107061727</v>
+        <v>0.01283202112338705</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2705,13 +2705,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.1760555575539664</v>
+        <v>0.176795973494158</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1760555575539664</v>
+        <v>0.176795973494158</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-0.1760555575539664</v>
+        <v>-0.176795973494158</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2770,13 +2770,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.05778714825231409</v>
+        <v>0.05803017679568236</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.05778714825231409</v>
+        <v>0.05803017679568236</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.05777689220490943</v>
+        <v>-0.05801992074827769</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.003193400854708576</v>
+        <v>0.00320683096125618</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.003193400854708576</v>
+        <v>0.00320683096125618</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.003183400854708576</v>
+        <v>-0.00319683096125618</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0001512941791903376</v>
+        <v>0.0001519304591435926</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0001512941791903376</v>
+        <v>0.0001519304591435926</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-4.22941791903376e-05</v>
+        <v>-4.293045914359264e-05</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>1.664515588609391e-05</v>
+        <v>1.671515844049359e-05</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>1.664515588609391e-05</v>
+        <v>1.671515844049359e-05</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-7.645155886093912e-06</v>
+        <v>-7.715158440493594e-06</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3099,13 +3099,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.513989001321894e-05</v>
+        <v>1.520356204978671e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.513989001321894e-05</v>
+        <v>1.520356204978671e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-1.381339430478294e-05</v>
+        <v>-1.387706634135071e-05</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>4.452777042111969e-06</v>
+        <v>4.471503557456923e-06</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>4.452777042111969e-06</v>
+        <v>4.471503557456923e-06</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-4.527770421119689e-07</v>
+        <v>-4.715035574569233e-07</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.271378979706272e-06</v>
+        <v>3.285137029589132e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.271378979706272e-06</v>
+        <v>3.285137029589132e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-3.271378979706272e-06</v>
+        <v>-3.285137029589132e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.36754867790434e-06</v>
+        <v>1.373300014892369e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.36754867790434e-06</v>
+        <v>1.373300014892369e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-5.452502184083397e-07</v>
+        <v>-5.510015553963693e-07</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.975689679250125e-07</v>
+        <v>1.983998602590648e-07</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.975689679250125e-07</v>
+        <v>1.983998602590648e-07</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-1.975689679250125e-07</v>
+        <v>-1.983998602590648e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -4687,11 +4687,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reference rate (effr), period avg</t>
+          <t>Reference rate (tbill_3m), period avg</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.03685357142857143</v>
       </c>
     </row>
     <row r="10">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.0371146726980668</v>
       </c>
     </row>
     <row r="11">
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.04055213531137732</v>
+        <v>0.04072545533915744</v>
       </c>
     </row>
     <row r="12">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-25.67866585083047</v>
+        <v>-23.9454655730293</v>
       </c>
     </row>
     <row r="13">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>475124.5953942272</v>
+        <v>442963.4499965028</v>
       </c>
     </row>
     <row r="15">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>7647253.492551014</v>
+        <v>7679414.637948738</v>
       </c>
     </row>
     <row r="17">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>475124.5953942272</v>
+        <v>442963.4499965028</v>
       </c>
     </row>
     <row r="19">
@@ -4791,7 +4791,7 @@
         <v>1000000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2763567.547045653</v>
+        <v>2795728.692443378</v>
       </c>
     </row>
     <row r="21">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>7486257.239294591</v>
+        <v>7518418.384692316</v>
       </c>
     </row>
     <row r="25">
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>7489988.518685198</v>
+        <v>7522149.664082923</v>
       </c>
     </row>
     <row r="28">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>10052985.99596801</v>
+        <v>10085147.14136574</v>
       </c>
     </row>
     <row r="31">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>7486257.239294591</v>
+        <v>7518418.384692316</v>
       </c>
     </row>
     <row r="32">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>effr</t>
+          <t>tbill_3m</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         <v>1</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0367</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03696750007901918</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>271745.3615508727</v>
+        <v>272505.1331893649</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>365045.1446174522</v>
+        <v>365804.9162559443</v>
       </c>
     </row>
     <row r="7">
@@ -5462,16 +5462,16 @@
         <v>1</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>267134.214574907</v>
+        <v>268400.3839424823</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>358933.3596232593</v>
+        <v>360199.5289908347</v>
       </c>
     </row>
     <row r="8">
@@ -5511,16 +5511,16 @@
         <v>1</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>270718.1201947443</v>
+        <v>271984.2895623196</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>362630.5695722945</v>
+        <v>363896.7389398698</v>
       </c>
     </row>
     <row r="9">
@@ -5560,16 +5560,16 @@
         <v>1</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>271294.5333121629</v>
+        <v>272560.7026797382</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>362837.1153855179</v>
+        <v>364103.2847530931</v>
       </c>
     </row>
     <row r="10">
@@ -5609,16 +5609,16 @@
         <v>1</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0367</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03696750007901918</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>262626.3951698382</v>
+        <v>263386.1668083303</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>352285.4117331658</v>
+        <v>353045.183371658</v>
       </c>
     </row>
     <row r="11">
@@ -5658,16 +5658,16 @@
         <v>1</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>259059.7101727402</v>
+        <v>260072.6923424415</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>343865.6754166156</v>
+        <v>344878.657586317</v>
       </c>
     </row>
     <row r="12">
@@ -5707,16 +5707,16 @@
         <v>1</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>258910.4751153023</v>
+        <v>259923.4572850037</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>342602.4304809652</v>
+        <v>343615.4126506665</v>
       </c>
     </row>
     <row r="13">
@@ -5756,16 +5756,16 @@
         <v>1</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>260275.2254159482</v>
+        <v>261288.2075856496</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>342600.8001298214</v>
+        <v>343613.7822995228</v>
       </c>
     </row>
     <row r="14">
@@ -5805,16 +5805,16 @@
         <v>1</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>273315.1784996446</v>
+        <v>274581.3478672199</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>356947.1621907688</v>
+        <v>358213.3315583441</v>
       </c>
     </row>
     <row r="15">
@@ -5854,16 +5854,16 @@
         <v>1</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>275296.5746392221</v>
+        <v>276562.7440067974</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>358994.0779206661</v>
+        <v>360260.2472882413</v>
       </c>
     </row>
     <row r="16">
@@ -5903,16 +5903,16 @@
         <v>1</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03725500007901918</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>278135.3942824989</v>
+        <v>279654.7275183876</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>363349.5738365015</v>
+        <v>364868.9070723901</v>
       </c>
     </row>
     <row r="17">
@@ -5952,16 +5952,16 @@
         <v>1</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03725500007901918</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>278759.5527566056</v>
+        <v>280278.8859924942</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>362299.4055865003</v>
+        <v>363818.738822389</v>
       </c>
     </row>
     <row r="18">
@@ -6001,16 +6001,16 @@
         <v>1</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>281019.9091966764</v>
+        <v>282032.8913663778</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>363695.0519874501</v>
+        <v>364708.0341571515</v>
       </c>
     </row>
     <row r="19">
@@ -6050,16 +6050,16 @@
         <v>1</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>276469.5665485744</v>
+        <v>277482.5487182758</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>360040.4861536592</v>
+        <v>361053.4683233606</v>
       </c>
     </row>
     <row r="20">
@@ -6099,16 +6099,16 @@
         <v>1</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>273156.8445600395</v>
+        <v>274169.8267297408</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>356395.9764575384</v>
+        <v>357408.9586272397</v>
       </c>
     </row>
     <row r="21">
@@ -6148,16 +6148,16 @@
         <v>1</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>282384.3186801649</v>
+        <v>283397.3008498663</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>364976.4952377997</v>
+        <v>365989.477407501</v>
       </c>
     </row>
     <row r="22">
@@ -6197,16 +6197,16 @@
         <v>1</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>280950.2860943094</v>
+        <v>282216.4554618847</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>365220.1550558825</v>
+        <v>366486.3244234578</v>
       </c>
     </row>
     <row r="23">
@@ -6246,16 +6246,16 @@
         <v>1</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03725500007901918</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>277542.8851611703</v>
+        <v>279062.218397059</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>361833.5569561925</v>
+        <v>363352.8901920812</v>
       </c>
     </row>
     <row r="24">
@@ -6295,16 +6295,16 @@
         <v>1</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>273601.6979060001</v>
+        <v>274867.8672735754</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>362162.940994632</v>
+        <v>363429.1103622073</v>
       </c>
     </row>
     <row r="25">
@@ -6344,16 +6344,16 @@
         <v>1</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>276332.9016689478</v>
+        <v>277599.0710365231</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>364936.3557712165</v>
+        <v>366202.5251387918</v>
       </c>
     </row>
     <row r="26">
@@ -6393,16 +6393,16 @@
         <v>1</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>277874.847798013</v>
+        <v>279141.0171655883</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>365215.6623250113</v>
+        <v>366481.8316925866</v>
       </c>
     </row>
     <row r="27">
@@ -6442,16 +6442,16 @@
         <v>1</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>277353.3566874388</v>
+        <v>278619.5260550141</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>364524.1393745443</v>
+        <v>365790.3087421195</v>
       </c>
     </row>
     <row r="28">
@@ -6491,16 +6491,16 @@
         <v>1</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>274703.3213502006</v>
+        <v>275969.4907177759</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>363114.1247107522</v>
+        <v>364380.2940783274</v>
       </c>
     </row>
     <row r="29">
@@ -6540,16 +6540,16 @@
         <v>1</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>272662.690574617</v>
+        <v>273928.8599421923</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>358725.7219450316</v>
+        <v>359991.8913126069</v>
       </c>
     </row>
     <row r="30">
@@ -6589,16 +6589,16 @@
         <v>1</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>272819.0757085824</v>
+        <v>274085.2450761577</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>356847.4829846853</v>
+        <v>358113.6523522606</v>
       </c>
     </row>
     <row r="31">
@@ -6638,16 +6638,16 @@
         <v>1</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>272598.6620706317</v>
+        <v>273611.6442403331</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>356243.3116253272</v>
+        <v>357256.2937950286</v>
       </c>
     </row>
     <row r="32">
@@ -6687,16 +6687,16 @@
         <v>1</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0367</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03696750007901918</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>268964.3774751638</v>
+        <v>269724.149113656</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>353646.0304370871</v>
+        <v>354405.8020755793</v>
       </c>
     </row>
     <row r="33">
@@ -6736,16 +6736,16 @@
         <v>1</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0367</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.03668000007901918</v>
+        <v>0.03696750007901918</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>281548.015385997</v>
+        <v>282307.7870244891</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>363017.777457673</v>
+        <v>363777.5490961652</v>
       </c>
     </row>
     <row r="35">
@@ -6767,10 +6767,10 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" s="12" t="n">
-        <v>7647253.492551014</v>
+        <v>7679414.637948738</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>10052985.99596801</v>
+        <v>10085147.14136574</v>
       </c>
     </row>
   </sheetData>

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1022253.36</v>
+        <v>1009112.93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11428640.93677005</v>
+        <v>11415500.50677005</v>
       </c>
     </row>
     <row r="9">

--- a/reports/spark/2026-02/spark_settlement_february_2026.xlsx
+++ b/reports/spark/2026-02/spark_settlement_february_2026.xlsx
@@ -4677,7 +4677,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base rate (BR = SSR + 30bps), period avg</t>
+          <t>Base rate (BR = SSR (+) spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
@@ -4896,7 +4896,7 @@
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+          <t>sUSDS spread (Curve LP + PSM3) — the BR−SSR spread (30 bps; 20 bps from 2026-07-23) × value, integrated daily, deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + spread nets to zero economically.</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tbill_3m</t>
+          <t>tbill_3m→sofr@2026-07-23</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
+          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>
